--- a/research/traditional_assets/database/data/colombia/colombia_steel.xlsx
+++ b/research/traditional_assets/database/data/colombia/colombia_steel.xlsx
@@ -1266,7 +1266,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Z101"/>
+  <dimension ref="A1:Z100"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1403,22 +1403,22 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="B2">
-        <v>0.1132565372525995</v>
+        <v>0.1128893893722155</v>
       </c>
       <c r="C2">
-        <v>108.224897639817</v>
+        <v>107.4971661025417</v>
       </c>
       <c r="D2">
-        <v>101.464897639817</v>
+        <v>102.0201661025417</v>
       </c>
       <c r="E2">
-        <v>-73</v>
+        <v>-71.717</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>1.283</v>
       </c>
       <c r="G2">
         <v>6.76</v>
@@ -1439,28 +1439,28 @@
         <v>32.13333333333334</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>0.06453490000000001</v>
       </c>
       <c r="N2">
-        <v>32.13333333333334</v>
+        <v>32.06879843333334</v>
       </c>
       <c r="O2">
-        <v>11.24666666666667</v>
+        <v>11.22407945166667</v>
       </c>
       <c r="P2">
-        <v>20.88666666666667</v>
+        <v>20.84471898166667</v>
       </c>
       <c r="Q2">
-        <v>41.58666666666667</v>
+        <v>41.54471898166668</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>0.0101010101010101</v>
       </c>
       <c r="S2">
-        <v>0.1132565372525995</v>
+        <v>0.1136994337093085</v>
       </c>
       <c r="T2">
-        <v>0.9815748103161357</v>
+        <v>0.9880194934141711</v>
       </c>
       <c r="U2">
         <v>0.0503</v>
@@ -1477,7 +1477,7 @@
         </is>
       </c>
       <c r="Y2">
-        <v>10000000</v>
+        <v>497.9217963200275</v>
       </c>
       <c r="Z2">
         <v>0</v>
@@ -1485,22 +1485,22 @@
     </row>
     <row r="3">
       <c r="A3">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="B3">
-        <v>0.1128893893722155</v>
+        <v>0.1125222414918313</v>
       </c>
       <c r="C3">
-        <v>107.4971661025417</v>
+        <v>106.7755454402783</v>
       </c>
       <c r="D3">
-        <v>102.0201661025417</v>
+        <v>102.5815454402783</v>
       </c>
       <c r="E3">
-        <v>-71.717</v>
+        <v>-70.434</v>
       </c>
       <c r="F3">
-        <v>1.283</v>
+        <v>2.566</v>
       </c>
       <c r="G3">
         <v>6.76</v>
@@ -1521,28 +1521,28 @@
         <v>32.13333333333334</v>
       </c>
       <c r="M3">
-        <v>0.06453490000000001</v>
+        <v>0.1290698</v>
       </c>
       <c r="N3">
-        <v>32.06879843333334</v>
+        <v>32.00426353333334</v>
       </c>
       <c r="O3">
-        <v>11.22407945166667</v>
+        <v>11.20149223666667</v>
       </c>
       <c r="P3">
-        <v>20.84471898166667</v>
+        <v>20.80277129666667</v>
       </c>
       <c r="Q3">
-        <v>41.54471898166668</v>
+        <v>41.50277129666667</v>
       </c>
       <c r="R3">
-        <v>0.0101010101010101</v>
+        <v>0.02040816326530612</v>
       </c>
       <c r="S3">
-        <v>0.1136994337093085</v>
+        <v>0.1141513688692156</v>
       </c>
       <c r="T3">
-        <v>0.9880194934141711</v>
+        <v>0.994595700657064</v>
       </c>
       <c r="U3">
         <v>0.0503</v>
@@ -1559,7 +1559,7 @@
         </is>
       </c>
       <c r="Y3">
-        <v>497.9217963200275</v>
+        <v>248.9608981600137</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1567,22 +1567,22 @@
     </row>
     <row r="4">
       <c r="A4">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="B4">
-        <v>0.1125222414918313</v>
+        <v>0.1121550936114472</v>
       </c>
       <c r="C4">
-        <v>106.7755454402783</v>
+        <v>106.0601370888631</v>
       </c>
       <c r="D4">
-        <v>102.5815454402783</v>
+        <v>103.1491370888631</v>
       </c>
       <c r="E4">
-        <v>-70.434</v>
+        <v>-69.151</v>
       </c>
       <c r="F4">
-        <v>2.566</v>
+        <v>3.849</v>
       </c>
       <c r="G4">
         <v>6.76</v>
@@ -1603,28 +1603,28 @@
         <v>32.13333333333334</v>
       </c>
       <c r="M4">
-        <v>0.1290698</v>
+        <v>0.1936047</v>
       </c>
       <c r="N4">
-        <v>32.00426353333334</v>
+        <v>31.93972863333334</v>
       </c>
       <c r="O4">
-        <v>11.20149223666667</v>
+        <v>11.17890502166667</v>
       </c>
       <c r="P4">
-        <v>20.80277129666667</v>
+        <v>20.76082361166667</v>
       </c>
       <c r="Q4">
-        <v>41.50277129666667</v>
+        <v>41.46082361166667</v>
       </c>
       <c r="R4">
-        <v>0.02040816326530612</v>
+        <v>0.03092783505154639</v>
       </c>
       <c r="S4">
-        <v>0.1141513688692156</v>
+        <v>0.1146126222798425</v>
       </c>
       <c r="T4">
-        <v>0.994595700657064</v>
+        <v>1.001307499801872</v>
       </c>
       <c r="U4">
         <v>0.0503</v>
@@ -1641,7 +1641,7 @@
         </is>
       </c>
       <c r="Y4">
-        <v>248.9608981600137</v>
+        <v>165.9739321066758</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -1649,22 +1649,22 @@
     </row>
     <row r="5">
       <c r="A5">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="B5">
-        <v>0.1121550936114472</v>
+        <v>0.1117879457310631</v>
       </c>
       <c r="C5">
-        <v>106.0601370888631</v>
+        <v>105.3510447416331</v>
       </c>
       <c r="D5">
-        <v>103.1491370888631</v>
+        <v>103.7230447416331</v>
       </c>
       <c r="E5">
-        <v>-69.151</v>
+        <v>-67.86799999999999</v>
       </c>
       <c r="F5">
-        <v>3.849</v>
+        <v>5.132000000000001</v>
       </c>
       <c r="G5">
         <v>6.76</v>
@@ -1685,28 +1685,28 @@
         <v>32.13333333333334</v>
       </c>
       <c r="M5">
-        <v>0.1936047</v>
+        <v>0.2581396</v>
       </c>
       <c r="N5">
-        <v>31.93972863333334</v>
+        <v>31.87519373333334</v>
       </c>
       <c r="O5">
-        <v>11.17890502166667</v>
+        <v>11.15631780666667</v>
       </c>
       <c r="P5">
-        <v>20.76082361166667</v>
+        <v>20.71887592666667</v>
       </c>
       <c r="Q5">
-        <v>41.46082361166667</v>
+        <v>41.41887592666667</v>
       </c>
       <c r="R5">
-        <v>0.03092783505154639</v>
+        <v>0.04166666666666667</v>
       </c>
       <c r="S5">
-        <v>0.1146126222798425</v>
+        <v>0.1150834851365241</v>
       </c>
       <c r="T5">
-        <v>1.001307499801872</v>
+        <v>1.008159128095531</v>
       </c>
       <c r="U5">
         <v>0.0503</v>
@@ -1723,7 +1723,7 @@
         </is>
       </c>
       <c r="Y5">
-        <v>165.9739321066758</v>
+        <v>124.4804490800068</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -1731,22 +1731,22 @@
     </row>
     <row r="6">
       <c r="A6">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="B6">
-        <v>0.1117879457310631</v>
+        <v>0.111420797850679</v>
       </c>
       <c r="C6">
-        <v>105.3510447416331</v>
+        <v>104.6483744125787</v>
       </c>
       <c r="D6">
-        <v>103.7230447416331</v>
+        <v>104.3033744125787</v>
       </c>
       <c r="E6">
-        <v>-67.86799999999999</v>
+        <v>-66.58499999999999</v>
       </c>
       <c r="F6">
-        <v>5.132000000000001</v>
+        <v>6.415000000000001</v>
       </c>
       <c r="G6">
         <v>6.76</v>
@@ -1767,28 +1767,28 @@
         <v>32.13333333333334</v>
       </c>
       <c r="M6">
-        <v>0.2581396</v>
+        <v>0.3226745</v>
       </c>
       <c r="N6">
-        <v>31.87519373333334</v>
+        <v>31.81065883333334</v>
       </c>
       <c r="O6">
-        <v>11.15631780666667</v>
+        <v>11.13373059166667</v>
       </c>
       <c r="P6">
-        <v>20.71887592666667</v>
+        <v>20.67692824166667</v>
       </c>
       <c r="Q6">
-        <v>41.41887592666667</v>
+        <v>41.37692824166668</v>
       </c>
       <c r="R6">
-        <v>0.04166666666666667</v>
+        <v>0.05263157894736843</v>
       </c>
       <c r="S6">
-        <v>0.1150834851365241</v>
+        <v>0.1155642608954516</v>
       </c>
       <c r="T6">
-        <v>1.008159128095531</v>
+        <v>1.015155001195372</v>
       </c>
       <c r="U6">
         <v>0.0503</v>
@@ -1805,7 +1805,7 @@
         </is>
       </c>
       <c r="Y6">
-        <v>124.4804490800068</v>
+        <v>99.58435926400547</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -1813,22 +1813,22 @@
     </row>
     <row r="7">
       <c r="A7">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="B7">
-        <v>0.111420797850679</v>
+        <v>0.1110536499702949</v>
       </c>
       <c r="C7">
-        <v>104.6483744125787</v>
+        <v>103.95223450163</v>
       </c>
       <c r="D7">
-        <v>104.3033744125787</v>
+        <v>104.89023450163</v>
       </c>
       <c r="E7">
-        <v>-66.58499999999999</v>
+        <v>-65.30199999999999</v>
       </c>
       <c r="F7">
-        <v>6.415000000000001</v>
+        <v>7.698000000000001</v>
       </c>
       <c r="G7">
         <v>6.76</v>
@@ -1849,28 +1849,28 @@
         <v>32.13333333333334</v>
       </c>
       <c r="M7">
-        <v>0.3226745</v>
+        <v>0.3872094</v>
       </c>
       <c r="N7">
-        <v>31.81065883333334</v>
+        <v>31.74612393333334</v>
       </c>
       <c r="O7">
-        <v>11.13373059166667</v>
+        <v>11.11114337666667</v>
       </c>
       <c r="P7">
-        <v>20.67692824166667</v>
+        <v>20.63498055666667</v>
       </c>
       <c r="Q7">
-        <v>41.37692824166668</v>
+        <v>41.33498055666667</v>
       </c>
       <c r="R7">
-        <v>0.05263157894736843</v>
+        <v>0.06382978723404256</v>
       </c>
       <c r="S7">
-        <v>0.1155642608954516</v>
+        <v>0.1160552659258457</v>
       </c>
       <c r="T7">
-        <v>1.015155001195372</v>
+        <v>1.022299722659039</v>
       </c>
       <c r="U7">
         <v>0.0503</v>
@@ -1887,7 +1887,7 @@
         </is>
       </c>
       <c r="Y7">
-        <v>99.58435926400547</v>
+        <v>82.98696605333791</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -1895,22 +1895,22 @@
     </row>
     <row r="8">
       <c r="A8">
-        <v>0.06</v>
+        <v>0.06999999999999999</v>
       </c>
       <c r="B8">
-        <v>0.1110536499702949</v>
+        <v>0.1106865020899108</v>
       </c>
       <c r="C8">
-        <v>103.95223450163</v>
+        <v>103.262735862158</v>
       </c>
       <c r="D8">
-        <v>104.89023450163</v>
+        <v>105.483735862158</v>
       </c>
       <c r="E8">
-        <v>-65.30199999999999</v>
+        <v>-64.01900000000001</v>
       </c>
       <c r="F8">
-        <v>7.698</v>
+        <v>8.981</v>
       </c>
       <c r="G8">
         <v>6.76</v>
@@ -1931,28 +1931,28 @@
         <v>32.13333333333334</v>
       </c>
       <c r="M8">
-        <v>0.3872094</v>
+        <v>0.4517443</v>
       </c>
       <c r="N8">
-        <v>31.74612393333334</v>
+        <v>31.68158903333334</v>
       </c>
       <c r="O8">
-        <v>11.11114337666667</v>
+        <v>11.08855616166667</v>
       </c>
       <c r="P8">
-        <v>20.63498055666667</v>
+        <v>20.59303287166667</v>
       </c>
       <c r="Q8">
-        <v>41.33498055666667</v>
+        <v>41.29303287166667</v>
       </c>
       <c r="R8">
-        <v>0.06382978723404255</v>
+        <v>0.07526881720430106</v>
       </c>
       <c r="S8">
-        <v>0.1160552659258457</v>
+        <v>0.1165568302042052</v>
       </c>
       <c r="T8">
-        <v>1.022299722659039</v>
+        <v>1.029598094046656</v>
       </c>
       <c r="U8">
         <v>0.0503</v>
@@ -1969,7 +1969,7 @@
         </is>
       </c>
       <c r="Y8">
-        <v>82.98696605333791</v>
+        <v>71.13168518857535</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -1977,22 +1977,22 @@
     </row>
     <row r="9">
       <c r="A9">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="B9">
-        <v>0.1106865020899108</v>
+        <v>0.1103193542095268</v>
       </c>
       <c r="C9">
-        <v>103.262735862158</v>
+        <v>102.5799918707817</v>
       </c>
       <c r="D9">
-        <v>105.483735862158</v>
+        <v>106.0839918707816</v>
       </c>
       <c r="E9">
-        <v>-64.01900000000001</v>
+        <v>-62.736</v>
       </c>
       <c r="F9">
-        <v>8.981000000000002</v>
+        <v>10.264</v>
       </c>
       <c r="G9">
         <v>6.76</v>
@@ -2013,28 +2013,28 @@
         <v>32.13333333333334</v>
       </c>
       <c r="M9">
-        <v>0.4517443</v>
+        <v>0.5162792</v>
       </c>
       <c r="N9">
-        <v>31.68158903333334</v>
+        <v>31.61705413333334</v>
       </c>
       <c r="O9">
-        <v>11.08855616166667</v>
+        <v>11.06596894666667</v>
       </c>
       <c r="P9">
-        <v>20.59303287166667</v>
+        <v>20.55108518666667</v>
       </c>
       <c r="Q9">
-        <v>41.29303287166667</v>
+        <v>41.25108518666667</v>
       </c>
       <c r="R9">
-        <v>0.07526881720430109</v>
+        <v>0.08695652173913043</v>
       </c>
       <c r="S9">
-        <v>0.1165568302042052</v>
+        <v>0.1170692980538334</v>
       </c>
       <c r="T9">
-        <v>1.029598094046656</v>
+        <v>1.03705512568183</v>
       </c>
       <c r="U9">
         <v>0.0503</v>
@@ -2051,7 +2051,7 @@
         </is>
       </c>
       <c r="Y9">
-        <v>71.13168518857535</v>
+        <v>62.24022454000342</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2059,22 +2059,22 @@
     </row>
     <row r="10">
       <c r="A10">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="B10">
-        <v>0.1103193542095268</v>
+        <v>0.1099522063291427</v>
       </c>
       <c r="C10">
-        <v>102.5799918707817</v>
+        <v>101.9041184995714</v>
       </c>
       <c r="D10">
-        <v>106.0839918707816</v>
+        <v>106.6911184995714</v>
       </c>
       <c r="E10">
-        <v>-62.736</v>
+        <v>-61.453</v>
       </c>
       <c r="F10">
-        <v>10.264</v>
+        <v>11.547</v>
       </c>
       <c r="G10">
         <v>6.76</v>
@@ -2095,28 +2095,28 @@
         <v>32.13333333333334</v>
       </c>
       <c r="M10">
-        <v>0.5162792</v>
+        <v>0.5808141</v>
       </c>
       <c r="N10">
-        <v>31.61705413333334</v>
+        <v>31.55251923333334</v>
       </c>
       <c r="O10">
-        <v>11.06596894666667</v>
+        <v>11.04338173166667</v>
       </c>
       <c r="P10">
-        <v>20.55108518666667</v>
+        <v>20.50913750166667</v>
       </c>
       <c r="Q10">
-        <v>41.25108518666667</v>
+        <v>41.20913750166667</v>
       </c>
       <c r="R10">
-        <v>0.08695652173913043</v>
+        <v>0.0989010989010989</v>
       </c>
       <c r="S10">
-        <v>0.1170692980538334</v>
+        <v>0.1175930289331238</v>
       </c>
       <c r="T10">
-        <v>1.03705512568183</v>
+        <v>1.044676048122173</v>
       </c>
       <c r="U10">
         <v>0.0503</v>
@@ -2133,7 +2133,7 @@
         </is>
       </c>
       <c r="Y10">
-        <v>62.24022454000342</v>
+        <v>55.32464403555861</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2141,22 +2141,22 @@
     </row>
     <row r="11">
       <c r="A11">
-        <v>0.09</v>
+        <v>0.09999999999999999</v>
       </c>
       <c r="B11">
-        <v>0.1099522063291427</v>
+        <v>0.1095850584487586</v>
       </c>
       <c r="C11">
-        <v>101.9041184995714</v>
+        <v>101.2352343907467</v>
       </c>
       <c r="D11">
-        <v>106.6911184995714</v>
+        <v>107.3052343907467</v>
       </c>
       <c r="E11">
-        <v>-61.453</v>
+        <v>-60.17</v>
       </c>
       <c r="F11">
-        <v>11.547</v>
+        <v>12.83</v>
       </c>
       <c r="G11">
         <v>6.76</v>
@@ -2177,28 +2177,28 @@
         <v>32.13333333333334</v>
       </c>
       <c r="M11">
-        <v>0.5808141</v>
+        <v>0.645349</v>
       </c>
       <c r="N11">
-        <v>31.55251923333334</v>
+        <v>31.48798433333334</v>
       </c>
       <c r="O11">
-        <v>11.04338173166667</v>
+        <v>11.02079451666667</v>
       </c>
       <c r="P11">
-        <v>20.50913750166667</v>
+        <v>20.46718981666667</v>
       </c>
       <c r="Q11">
-        <v>41.20913750166667</v>
+        <v>41.16718981666667</v>
       </c>
       <c r="R11">
-        <v>0.0989010989010989</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="S11">
-        <v>0.1175930289331238</v>
+        <v>0.1181283982763984</v>
       </c>
       <c r="T11">
-        <v>1.044676048122173</v>
+        <v>1.052466324394523</v>
       </c>
       <c r="U11">
         <v>0.0503</v>
@@ -2215,7 +2215,7 @@
         </is>
       </c>
       <c r="Y11">
-        <v>55.32464403555861</v>
+        <v>49.79217963200275</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2223,22 +2223,22 @@
     </row>
     <row r="12">
       <c r="A12">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="B12">
-        <v>0.1095850584487586</v>
+        <v>0.1092179105683745</v>
       </c>
       <c r="C12">
-        <v>101.2352343907467</v>
+        <v>100.5734609339676</v>
       </c>
       <c r="D12">
-        <v>107.3052343907467</v>
+        <v>107.9264609339676</v>
       </c>
       <c r="E12">
-        <v>-60.17</v>
+        <v>-58.887</v>
       </c>
       <c r="F12">
-        <v>12.83</v>
+        <v>14.113</v>
       </c>
       <c r="G12">
         <v>6.76</v>
@@ -2259,28 +2259,28 @@
         <v>32.13333333333334</v>
       </c>
       <c r="M12">
-        <v>0.6453490000000001</v>
+        <v>0.7098839</v>
       </c>
       <c r="N12">
-        <v>31.48798433333334</v>
+        <v>31.42344943333334</v>
       </c>
       <c r="O12">
-        <v>11.02079451666667</v>
+        <v>10.99820730166667</v>
       </c>
       <c r="P12">
-        <v>20.46718981666667</v>
+        <v>20.42524213166667</v>
       </c>
       <c r="Q12">
-        <v>41.16718981666667</v>
+        <v>41.12524213166667</v>
       </c>
       <c r="R12">
-        <v>0.1111111111111111</v>
+        <v>0.1235955056179775</v>
       </c>
       <c r="S12">
-        <v>0.1181283982763984</v>
+        <v>0.118675798391432</v>
       </c>
       <c r="T12">
-        <v>1.052466324394523</v>
+        <v>1.060431663055016</v>
       </c>
       <c r="U12">
         <v>0.0503</v>
@@ -2297,7 +2297,7 @@
         </is>
       </c>
       <c r="Y12">
-        <v>49.79217963200274</v>
+        <v>45.26561784727522</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2305,22 +2305,22 @@
     </row>
     <row r="13">
       <c r="A13">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="B13">
-        <v>0.1092179105683745</v>
+        <v>0.1088507626879903</v>
       </c>
       <c r="C13">
-        <v>100.5734609339676</v>
+        <v>99.91892234632753</v>
       </c>
       <c r="D13">
-        <v>107.9264609339676</v>
+        <v>108.5549223463275</v>
       </c>
       <c r="E13">
-        <v>-58.887</v>
+        <v>-57.604</v>
       </c>
       <c r="F13">
-        <v>14.113</v>
+        <v>15.396</v>
       </c>
       <c r="G13">
         <v>6.76</v>
@@ -2341,28 +2341,28 @@
         <v>32.13333333333334</v>
       </c>
       <c r="M13">
-        <v>0.7098839</v>
+        <v>0.7744188</v>
       </c>
       <c r="N13">
-        <v>31.42344943333334</v>
+        <v>31.35891453333334</v>
       </c>
       <c r="O13">
-        <v>10.99820730166667</v>
+        <v>10.97562008666667</v>
       </c>
       <c r="P13">
-        <v>20.42524213166667</v>
+        <v>20.38329444666667</v>
       </c>
       <c r="Q13">
-        <v>41.12524213166667</v>
+        <v>41.08329444666667</v>
       </c>
       <c r="R13">
-        <v>0.1235955056179775</v>
+        <v>0.1363636363636364</v>
       </c>
       <c r="S13">
-        <v>0.118675798391432</v>
+        <v>0.1192356394181709</v>
       </c>
       <c r="T13">
-        <v>1.060431663055016</v>
+        <v>1.068578032139611</v>
       </c>
       <c r="U13">
         <v>0.0503</v>
@@ -2379,7 +2379,7 @@
         </is>
       </c>
       <c r="Y13">
-        <v>45.26561784727522</v>
+        <v>41.49348302666895</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2387,22 +2387,22 @@
     </row>
     <row r="14">
       <c r="A14">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="B14">
-        <v>0.1088507626879903</v>
+        <v>0.1084836148076063</v>
       </c>
       <c r="C14">
-        <v>99.91892234632753</v>
+        <v>99.27174575515676</v>
       </c>
       <c r="D14">
-        <v>108.5549223463275</v>
+        <v>109.1907457551568</v>
       </c>
       <c r="E14">
-        <v>-57.604</v>
+        <v>-56.321</v>
       </c>
       <c r="F14">
-        <v>15.396</v>
+        <v>16.679</v>
       </c>
       <c r="G14">
         <v>6.76</v>
@@ -2423,28 +2423,28 @@
         <v>32.13333333333334</v>
       </c>
       <c r="M14">
-        <v>0.7744188</v>
+        <v>0.8389537</v>
       </c>
       <c r="N14">
-        <v>31.35891453333334</v>
+        <v>31.29437963333334</v>
       </c>
       <c r="O14">
-        <v>10.97562008666667</v>
+        <v>10.95303287166667</v>
       </c>
       <c r="P14">
-        <v>20.38329444666667</v>
+        <v>20.34134676166667</v>
       </c>
       <c r="Q14">
-        <v>41.08329444666667</v>
+        <v>41.04134676166667</v>
       </c>
       <c r="R14">
-        <v>0.1363636363636364</v>
+        <v>0.1494252873563219</v>
       </c>
       <c r="S14">
-        <v>0.1192356394181709</v>
+        <v>0.1198083503535704</v>
       </c>
       <c r="T14">
-        <v>1.068578032139611</v>
+        <v>1.076911674076726</v>
       </c>
       <c r="U14">
         <v>0.0503</v>
@@ -2461,7 +2461,7 @@
         </is>
       </c>
       <c r="Y14">
-        <v>41.49348302666895</v>
+        <v>38.30167664000211</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2469,22 +2469,22 @@
     </row>
     <row r="15">
       <c r="A15">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
       <c r="B15">
-        <v>0.1084836148076063</v>
+        <v>0.1081164669272222</v>
       </c>
       <c r="C15">
-        <v>99.27174575515676</v>
+        <v>98.63206128375349</v>
       </c>
       <c r="D15">
-        <v>109.1907457551568</v>
+        <v>109.8340612837535</v>
       </c>
       <c r="E15">
-        <v>-56.321</v>
+        <v>-55.038</v>
       </c>
       <c r="F15">
-        <v>16.679</v>
+        <v>17.962</v>
       </c>
       <c r="G15">
         <v>6.76</v>
@@ -2505,28 +2505,28 @@
         <v>32.13333333333334</v>
       </c>
       <c r="M15">
-        <v>0.8389537</v>
+        <v>0.9034886000000001</v>
       </c>
       <c r="N15">
-        <v>31.29437963333334</v>
+        <v>31.22984473333334</v>
       </c>
       <c r="O15">
-        <v>10.95303287166667</v>
+        <v>10.93044565666667</v>
       </c>
       <c r="P15">
-        <v>20.34134676166667</v>
+        <v>20.29939907666667</v>
       </c>
       <c r="Q15">
-        <v>41.04134676166667</v>
+        <v>40.99939907666668</v>
       </c>
       <c r="R15">
-        <v>0.1494252873563219</v>
+        <v>0.1627906976744186</v>
       </c>
       <c r="S15">
-        <v>0.1198083503535704</v>
+        <v>0.1203943801479327</v>
       </c>
       <c r="T15">
-        <v>1.076911674076726</v>
+        <v>1.085439121640285</v>
       </c>
       <c r="U15">
         <v>0.0503</v>
@@ -2543,7 +2543,7 @@
         </is>
       </c>
       <c r="Y15">
-        <v>38.30167664000211</v>
+        <v>35.56584259428767</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2551,22 +2551,22 @@
     </row>
     <row r="16">
       <c r="A16">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="B16">
-        <v>0.1081164669272222</v>
+        <v>0.1077493190468381</v>
       </c>
       <c r="C16">
-        <v>98.63206128375349</v>
+        <v>98.00000214016255</v>
       </c>
       <c r="D16">
-        <v>109.8340612837535</v>
+        <v>110.4850021401625</v>
       </c>
       <c r="E16">
-        <v>-55.038</v>
+        <v>-53.755</v>
       </c>
       <c r="F16">
-        <v>17.962</v>
+        <v>19.245</v>
       </c>
       <c r="G16">
         <v>6.76</v>
@@ -2587,28 +2587,28 @@
         <v>32.13333333333334</v>
       </c>
       <c r="M16">
-        <v>0.9034886000000001</v>
+        <v>0.9680235000000001</v>
       </c>
       <c r="N16">
-        <v>31.22984473333334</v>
+        <v>31.16530983333334</v>
       </c>
       <c r="O16">
-        <v>10.93044565666667</v>
+        <v>10.90785844166667</v>
       </c>
       <c r="P16">
-        <v>20.29939907666667</v>
+        <v>20.25745139166667</v>
       </c>
       <c r="Q16">
-        <v>40.99939907666668</v>
+        <v>40.95745139166667</v>
       </c>
       <c r="R16">
-        <v>0.1627906976744186</v>
+        <v>0.1764705882352942</v>
       </c>
       <c r="S16">
-        <v>0.1203943801479327</v>
+        <v>0.120994198878633</v>
       </c>
       <c r="T16">
-        <v>1.085439121640285</v>
+        <v>1.094167215028869</v>
       </c>
       <c r="U16">
         <v>0.0503</v>
@@ -2625,7 +2625,7 @@
         </is>
       </c>
       <c r="Y16">
-        <v>35.56584259428767</v>
+        <v>33.19478642133516</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -2633,22 +2633,22 @@
     </row>
     <row r="17">
       <c r="A17">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="B17">
-        <v>0.1077493190468381</v>
+        <v>0.107382171166454</v>
       </c>
       <c r="C17">
-        <v>98.00000214016255</v>
+        <v>97.37570470913093</v>
       </c>
       <c r="D17">
-        <v>110.4850021401625</v>
+        <v>111.1437047091309</v>
       </c>
       <c r="E17">
-        <v>-53.755</v>
+        <v>-52.47199999999999</v>
       </c>
       <c r="F17">
-        <v>19.245</v>
+        <v>20.528</v>
       </c>
       <c r="G17">
         <v>6.76</v>
@@ -2669,28 +2669,28 @@
         <v>32.13333333333334</v>
       </c>
       <c r="M17">
-        <v>0.9680235</v>
+        <v>1.0325584</v>
       </c>
       <c r="N17">
-        <v>31.16530983333334</v>
+        <v>31.10077493333334</v>
       </c>
       <c r="O17">
-        <v>10.90785844166667</v>
+        <v>10.88527122666667</v>
       </c>
       <c r="P17">
-        <v>20.25745139166667</v>
+        <v>20.21550370666667</v>
       </c>
       <c r="Q17">
-        <v>40.95745139166667</v>
+        <v>40.91550370666667</v>
       </c>
       <c r="R17">
-        <v>0.1764705882352941</v>
+        <v>0.1904761904761905</v>
       </c>
       <c r="S17">
-        <v>0.120994198878633</v>
+        <v>0.1216082990076833</v>
       </c>
       <c r="T17">
-        <v>1.094167215028869</v>
+        <v>1.1031031201648</v>
       </c>
       <c r="U17">
         <v>0.0503</v>
@@ -2707,7 +2707,7 @@
         </is>
       </c>
       <c r="Y17">
-        <v>33.19478642133516</v>
+        <v>31.12011227000171</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -2715,22 +2715,22 @@
     </row>
     <row r="18">
       <c r="A18">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
       <c r="B18">
-        <v>0.107382171166454</v>
+        <v>0.1070150232860699</v>
       </c>
       <c r="C18">
-        <v>97.37570470913093</v>
+        <v>96.7593086473717</v>
       </c>
       <c r="D18">
-        <v>111.1437047091309</v>
+        <v>111.8103086473717</v>
       </c>
       <c r="E18">
-        <v>-52.47199999999999</v>
+        <v>-51.18899999999999</v>
       </c>
       <c r="F18">
-        <v>20.528</v>
+        <v>21.811</v>
       </c>
       <c r="G18">
         <v>6.76</v>
@@ -2751,28 +2751,28 @@
         <v>32.13333333333334</v>
       </c>
       <c r="M18">
-        <v>1.0325584</v>
+        <v>1.0970933</v>
       </c>
       <c r="N18">
-        <v>31.10077493333334</v>
+        <v>31.03624003333334</v>
       </c>
       <c r="O18">
-        <v>10.88527122666667</v>
+        <v>10.86268401166667</v>
       </c>
       <c r="P18">
-        <v>20.21550370666667</v>
+        <v>20.17355602166667</v>
       </c>
       <c r="Q18">
-        <v>40.91550370666667</v>
+        <v>40.87355602166667</v>
       </c>
       <c r="R18">
-        <v>0.1904761904761905</v>
+        <v>0.2048192771084338</v>
       </c>
       <c r="S18">
-        <v>0.1216082990076833</v>
+        <v>0.1222371967302047</v>
       </c>
       <c r="T18">
-        <v>1.1031031201648</v>
+        <v>1.112254348316055</v>
       </c>
       <c r="U18">
         <v>0.0503</v>
@@ -2789,7 +2789,7 @@
         </is>
       </c>
       <c r="Y18">
-        <v>31.12011227000171</v>
+        <v>29.28951743058985</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -2797,22 +2797,22 @@
     </row>
     <row r="19">
       <c r="A19">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="B19">
-        <v>0.1070150232860699</v>
+        <v>0.1066478754056858</v>
       </c>
       <c r="C19">
-        <v>96.7593086473717</v>
+        <v>96.15095698227705</v>
       </c>
       <c r="D19">
-        <v>111.8103086473717</v>
+        <v>112.4849569822771</v>
       </c>
       <c r="E19">
-        <v>-51.18899999999999</v>
+        <v>-49.90599999999999</v>
       </c>
       <c r="F19">
-        <v>21.811</v>
+        <v>23.094</v>
       </c>
       <c r="G19">
         <v>6.76</v>
@@ -2833,28 +2833,28 @@
         <v>32.13333333333334</v>
       </c>
       <c r="M19">
-        <v>1.0970933</v>
+        <v>1.1616282</v>
       </c>
       <c r="N19">
-        <v>31.03624003333334</v>
+        <v>30.97170513333334</v>
       </c>
       <c r="O19">
-        <v>10.86268401166667</v>
+        <v>10.84009679666667</v>
       </c>
       <c r="P19">
-        <v>20.17355602166667</v>
+        <v>20.13160833666667</v>
       </c>
       <c r="Q19">
-        <v>40.87355602166667</v>
+        <v>40.83160833666668</v>
       </c>
       <c r="R19">
-        <v>0.2048192771084338</v>
+        <v>0.2195121951219512</v>
       </c>
       <c r="S19">
-        <v>0.1222371967302047</v>
+        <v>0.122881433421568</v>
       </c>
       <c r="T19">
-        <v>1.112254348316055</v>
+        <v>1.121628777153926</v>
       </c>
       <c r="U19">
         <v>0.0503</v>
@@ -2871,7 +2871,7 @@
         </is>
       </c>
       <c r="Y19">
-        <v>29.28951743058985</v>
+        <v>27.6623220177793</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -2879,22 +2879,22 @@
     </row>
     <row r="20">
       <c r="A20">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="B20">
-        <v>0.1066478754056858</v>
+        <v>0.1062807275253017</v>
       </c>
       <c r="C20">
-        <v>96.15095698227702</v>
+        <v>95.55079621422675</v>
       </c>
       <c r="D20">
-        <v>112.484956982277</v>
+        <v>113.1677962142268</v>
       </c>
       <c r="E20">
-        <v>-49.906</v>
+        <v>-48.623</v>
       </c>
       <c r="F20">
-        <v>23.094</v>
+        <v>24.377</v>
       </c>
       <c r="G20">
         <v>6.76</v>
@@ -2915,28 +2915,28 @@
         <v>32.13333333333334</v>
       </c>
       <c r="M20">
-        <v>1.1616282</v>
+        <v>1.2261631</v>
       </c>
       <c r="N20">
-        <v>30.97170513333334</v>
+        <v>30.90717023333334</v>
       </c>
       <c r="O20">
-        <v>10.84009679666667</v>
+        <v>10.81750958166667</v>
       </c>
       <c r="P20">
-        <v>20.13160833666667</v>
+        <v>20.08966065166667</v>
       </c>
       <c r="Q20">
-        <v>40.83160833666668</v>
+        <v>40.78966065166667</v>
       </c>
       <c r="R20">
-        <v>0.2195121951219512</v>
+        <v>0.2345679012345679</v>
       </c>
       <c r="S20">
-        <v>0.122881433421568</v>
+        <v>0.1235415771917305</v>
       </c>
       <c r="T20">
-        <v>1.121628777153926</v>
+        <v>1.13123467337051</v>
       </c>
       <c r="U20">
         <v>0.0503</v>
@@ -2953,7 +2953,7 @@
         </is>
       </c>
       <c r="Y20">
-        <v>27.6623220177793</v>
+        <v>26.20641033263302</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -2961,22 +2961,22 @@
     </row>
     <row r="21">
       <c r="A21">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
       <c r="B21">
-        <v>0.1062807275253017</v>
+        <v>0.1059135796449176</v>
       </c>
       <c r="C21">
-        <v>95.55079621422675</v>
+        <v>94.95897642264589</v>
       </c>
       <c r="D21">
-        <v>113.1677962142268</v>
+        <v>113.8589764226459</v>
       </c>
       <c r="E21">
-        <v>-48.623</v>
+        <v>-47.34</v>
       </c>
       <c r="F21">
-        <v>24.377</v>
+        <v>25.66</v>
       </c>
       <c r="G21">
         <v>6.76</v>
@@ -2997,28 +2997,28 @@
         <v>32.13333333333334</v>
       </c>
       <c r="M21">
-        <v>1.2261631</v>
+        <v>1.290698</v>
       </c>
       <c r="N21">
-        <v>30.90717023333334</v>
+        <v>30.84263533333334</v>
       </c>
       <c r="O21">
-        <v>10.81750958166667</v>
+        <v>10.79492236666667</v>
       </c>
       <c r="P21">
-        <v>20.08966065166667</v>
+        <v>20.04771296666667</v>
       </c>
       <c r="Q21">
-        <v>40.78966065166667</v>
+        <v>40.74771296666667</v>
       </c>
       <c r="R21">
-        <v>0.2345679012345679</v>
+        <v>0.25</v>
       </c>
       <c r="S21">
-        <v>0.1235415771917305</v>
+        <v>0.124218224556147</v>
       </c>
       <c r="T21">
-        <v>1.13123467337051</v>
+        <v>1.141080716992508</v>
       </c>
       <c r="U21">
         <v>0.0503</v>
@@ -3035,7 +3035,7 @@
         </is>
       </c>
       <c r="Y21">
-        <v>26.20641033263302</v>
+        <v>24.89608981600137</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3043,22 +3043,22 @@
     </row>
     <row r="22">
       <c r="A22">
-        <v>0.2</v>
+        <v>0.21</v>
       </c>
       <c r="B22">
-        <v>0.1059135796449176</v>
+        <v>0.1055464317645335</v>
       </c>
       <c r="C22">
-        <v>94.95897642264589</v>
+        <v>94.37565137597244</v>
       </c>
       <c r="D22">
-        <v>113.8589764226459</v>
+        <v>114.5586513759724</v>
       </c>
       <c r="E22">
-        <v>-47.34</v>
+        <v>-46.057</v>
       </c>
       <c r="F22">
-        <v>25.66</v>
+        <v>26.943</v>
       </c>
       <c r="G22">
         <v>6.76</v>
@@ -3079,28 +3079,28 @@
         <v>32.13333333333334</v>
       </c>
       <c r="M22">
-        <v>1.290698</v>
+        <v>1.3552329</v>
       </c>
       <c r="N22">
-        <v>30.84263533333334</v>
+        <v>30.77810043333334</v>
       </c>
       <c r="O22">
-        <v>10.79492236666667</v>
+        <v>10.77233515166667</v>
       </c>
       <c r="P22">
-        <v>20.04771296666667</v>
+        <v>20.00576528166667</v>
       </c>
       <c r="Q22">
-        <v>40.74771296666667</v>
+        <v>40.70576528166667</v>
       </c>
       <c r="R22">
-        <v>0.25</v>
+        <v>0.2658227848101266</v>
       </c>
       <c r="S22">
-        <v>0.124218224556147</v>
+        <v>0.1249120022335867</v>
       </c>
       <c r="T22">
-        <v>1.141080716992508</v>
+        <v>1.151176027541645</v>
       </c>
       <c r="U22">
         <v>0.0503</v>
@@ -3117,7 +3117,7 @@
         </is>
       </c>
       <c r="Y22">
-        <v>24.89608981600137</v>
+        <v>23.71056172952511</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3125,22 +3125,22 @@
     </row>
     <row r="23">
       <c r="A23">
-        <v>0.21</v>
+        <v>0.22</v>
       </c>
       <c r="B23">
-        <v>0.1055464317645335</v>
+        <v>0.1051792838841494</v>
       </c>
       <c r="C23">
-        <v>94.37565137597245</v>
+        <v>93.80097864570529</v>
       </c>
       <c r="D23">
-        <v>114.5586513759724</v>
+        <v>115.2669786457053</v>
       </c>
       <c r="E23">
-        <v>-46.057</v>
+        <v>-44.774</v>
       </c>
       <c r="F23">
-        <v>26.943</v>
+        <v>28.226</v>
       </c>
       <c r="G23">
         <v>6.76</v>
@@ -3161,28 +3161,28 @@
         <v>32.13333333333334</v>
       </c>
       <c r="M23">
-        <v>1.3552329</v>
+        <v>1.4197678</v>
       </c>
       <c r="N23">
-        <v>30.77810043333334</v>
+        <v>30.71356553333334</v>
       </c>
       <c r="O23">
-        <v>10.77233515166667</v>
+        <v>10.74974793666667</v>
       </c>
       <c r="P23">
-        <v>20.00576528166667</v>
+        <v>19.96381759666667</v>
       </c>
       <c r="Q23">
-        <v>40.70576528166667</v>
+        <v>40.66381759666668</v>
       </c>
       <c r="R23">
-        <v>0.2658227848101266</v>
+        <v>0.282051282051282</v>
       </c>
       <c r="S23">
-        <v>0.1249120022335867</v>
+        <v>0.1256235690822428</v>
       </c>
       <c r="T23">
-        <v>1.151176027541645</v>
+        <v>1.161530192207427</v>
       </c>
       <c r="U23">
         <v>0.0503</v>
@@ -3199,7 +3199,7 @@
         </is>
       </c>
       <c r="Y23">
-        <v>23.71056172952511</v>
+        <v>22.63280892363761</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3207,22 +3207,22 @@
     </row>
     <row r="24">
       <c r="A24">
-        <v>0.22</v>
+        <v>0.23</v>
       </c>
       <c r="B24">
-        <v>0.1051792838841494</v>
+        <v>0.1048121360037653</v>
       </c>
       <c r="C24">
-        <v>93.80097864570529</v>
+        <v>93.23511972470894</v>
       </c>
       <c r="D24">
-        <v>115.2669786457053</v>
+        <v>115.9841197247089</v>
       </c>
       <c r="E24">
-        <v>-44.774</v>
+        <v>-43.491</v>
       </c>
       <c r="F24">
-        <v>28.226</v>
+        <v>29.509</v>
       </c>
       <c r="G24">
         <v>6.76</v>
@@ -3243,28 +3243,28 @@
         <v>32.13333333333334</v>
       </c>
       <c r="M24">
-        <v>1.4197678</v>
+        <v>1.4843027</v>
       </c>
       <c r="N24">
-        <v>30.71356553333334</v>
+        <v>30.64903063333334</v>
       </c>
       <c r="O24">
-        <v>10.74974793666667</v>
+        <v>10.72716072166667</v>
       </c>
       <c r="P24">
-        <v>19.96381759666667</v>
+        <v>19.92186991166667</v>
       </c>
       <c r="Q24">
-        <v>40.66381759666668</v>
+        <v>40.62186991166667</v>
       </c>
       <c r="R24">
-        <v>0.282051282051282</v>
+        <v>0.2987012987012987</v>
       </c>
       <c r="S24">
-        <v>0.1256235690822428</v>
+        <v>0.1263536181867081</v>
       </c>
       <c r="T24">
-        <v>1.161530192207427</v>
+        <v>1.172153296215178</v>
       </c>
       <c r="U24">
         <v>0.0503</v>
@@ -3281,7 +3281,7 @@
         </is>
       </c>
       <c r="Y24">
-        <v>22.63280892363761</v>
+        <v>21.64877375304467</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3289,22 +3289,22 @@
     </row>
     <row r="25">
       <c r="A25">
-        <v>0.23</v>
+        <v>0.24</v>
       </c>
       <c r="B25">
-        <v>0.1048121360037653</v>
+        <v>0.1044449881233812</v>
       </c>
       <c r="C25">
-        <v>93.23511972470894</v>
+        <v>92.67824014996252</v>
       </c>
       <c r="D25">
-        <v>115.9841197247089</v>
+        <v>116.7102401499625</v>
       </c>
       <c r="E25">
-        <v>-43.491</v>
+        <v>-42.208</v>
       </c>
       <c r="F25">
-        <v>29.509</v>
+        <v>30.79200000000001</v>
       </c>
       <c r="G25">
         <v>6.76</v>
@@ -3325,28 +3325,28 @@
         <v>32.13333333333334</v>
       </c>
       <c r="M25">
-        <v>1.4843027</v>
+        <v>1.5488376</v>
       </c>
       <c r="N25">
-        <v>30.64903063333334</v>
+        <v>30.58449573333334</v>
       </c>
       <c r="O25">
-        <v>10.72716072166667</v>
+        <v>10.70457350666667</v>
       </c>
       <c r="P25">
-        <v>19.92186991166667</v>
+        <v>19.87992222666667</v>
       </c>
       <c r="Q25">
-        <v>40.62186991166667</v>
+        <v>40.57992222666667</v>
       </c>
       <c r="R25">
-        <v>0.2987012987012987</v>
+        <v>0.3157894736842106</v>
       </c>
       <c r="S25">
-        <v>0.1263536181867081</v>
+        <v>0.1271028791097121</v>
       </c>
       <c r="T25">
-        <v>1.172153296215178</v>
+        <v>1.183055955591553</v>
       </c>
       <c r="U25">
         <v>0.0503</v>
@@ -3363,7 +3363,7 @@
         </is>
       </c>
       <c r="Y25">
-        <v>21.64877375304467</v>
+        <v>20.74674151333448</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3371,22 +3371,22 @@
     </row>
     <row r="26">
       <c r="A26">
-        <v>0.24</v>
+        <v>0.25</v>
       </c>
       <c r="B26">
-        <v>0.1044449881233812</v>
+        <v>0.1040778402429971</v>
       </c>
       <c r="C26">
-        <v>92.67824014996252</v>
+        <v>92.13050962994852</v>
       </c>
       <c r="D26">
-        <v>116.7102401499625</v>
+        <v>117.4455096299485</v>
       </c>
       <c r="E26">
-        <v>-42.208</v>
+        <v>-40.925</v>
       </c>
       <c r="F26">
-        <v>30.792</v>
+        <v>32.075</v>
       </c>
       <c r="G26">
         <v>6.76</v>
@@ -3407,28 +3407,28 @@
         <v>32.13333333333334</v>
       </c>
       <c r="M26">
-        <v>1.5488376</v>
+        <v>1.6133725</v>
       </c>
       <c r="N26">
-        <v>30.58449573333334</v>
+        <v>30.51996083333334</v>
       </c>
       <c r="O26">
-        <v>10.70457350666667</v>
+        <v>10.68198629166667</v>
       </c>
       <c r="P26">
-        <v>19.87992222666667</v>
+        <v>19.83797454166667</v>
       </c>
       <c r="Q26">
-        <v>40.57992222666667</v>
+        <v>40.53797454166667</v>
       </c>
       <c r="R26">
-        <v>0.3157894736842105</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="S26">
-        <v>0.1271028791097121</v>
+        <v>0.1278721203239961</v>
       </c>
       <c r="T26">
-        <v>1.183055955591553</v>
+        <v>1.194249352551298</v>
       </c>
       <c r="U26">
         <v>0.0503</v>
@@ -3445,7 +3445,7 @@
         </is>
       </c>
       <c r="Y26">
-        <v>20.74674151333448</v>
+        <v>19.9168718528011</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3453,22 +3453,22 @@
     </row>
     <row r="27">
       <c r="A27">
-        <v>0.25</v>
+        <v>0.26</v>
       </c>
       <c r="B27">
-        <v>0.1040778402429971</v>
+        <v>0.103710692362613</v>
       </c>
       <c r="C27">
-        <v>92.13050962994852</v>
+        <v>91.59210217688735</v>
       </c>
       <c r="D27">
-        <v>117.4455096299485</v>
+        <v>118.1901021768874</v>
       </c>
       <c r="E27">
-        <v>-40.925</v>
+        <v>-39.642</v>
       </c>
       <c r="F27">
-        <v>32.075</v>
+        <v>33.358</v>
       </c>
       <c r="G27">
         <v>6.76</v>
@@ -3489,28 +3489,28 @@
         <v>32.13333333333334</v>
       </c>
       <c r="M27">
-        <v>1.6133725</v>
+        <v>1.6779074</v>
       </c>
       <c r="N27">
-        <v>30.51996083333334</v>
+        <v>30.45542593333334</v>
       </c>
       <c r="O27">
-        <v>10.68198629166667</v>
+        <v>10.65939907666667</v>
       </c>
       <c r="P27">
-        <v>19.83797454166667</v>
+        <v>19.79602685666667</v>
       </c>
       <c r="Q27">
-        <v>40.53797454166667</v>
+        <v>40.49602685666667</v>
       </c>
       <c r="R27">
-        <v>0.3333333333333333</v>
+        <v>0.3513513513513514</v>
       </c>
       <c r="S27">
-        <v>0.1278721203239961</v>
+        <v>0.1286621518413689</v>
       </c>
       <c r="T27">
-        <v>1.194249352551298</v>
+        <v>1.205745273753199</v>
       </c>
       <c r="U27">
         <v>0.0503</v>
@@ -3527,7 +3527,7 @@
         </is>
       </c>
       <c r="Y27">
-        <v>19.9168718528011</v>
+        <v>19.15083832000106</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3535,22 +3535,22 @@
     </row>
     <row r="28">
       <c r="A28">
-        <v>0.26</v>
+        <v>0.27</v>
       </c>
       <c r="B28">
-        <v>0.103710692362613</v>
+        <v>0.1033435444822289</v>
       </c>
       <c r="C28">
-        <v>91.59210217688735</v>
+        <v>91.06319624403372</v>
       </c>
       <c r="D28">
-        <v>118.1901021768874</v>
+        <v>118.9441962440337</v>
       </c>
       <c r="E28">
-        <v>-39.642</v>
+        <v>-38.35899999999999</v>
       </c>
       <c r="F28">
-        <v>33.358</v>
+        <v>34.64100000000001</v>
       </c>
       <c r="G28">
         <v>6.76</v>
@@ -3571,28 +3571,28 @@
         <v>32.13333333333334</v>
       </c>
       <c r="M28">
-        <v>1.6779074</v>
+        <v>1.7424423</v>
       </c>
       <c r="N28">
-        <v>30.45542593333334</v>
+        <v>30.39089103333334</v>
       </c>
       <c r="O28">
-        <v>10.65939907666667</v>
+        <v>10.63681186166667</v>
       </c>
       <c r="P28">
-        <v>19.79602685666667</v>
+        <v>19.75407917166667</v>
       </c>
       <c r="Q28">
-        <v>40.49602685666667</v>
+        <v>40.45407917166667</v>
       </c>
       <c r="R28">
-        <v>0.3513513513513514</v>
+        <v>0.3698630136986302</v>
       </c>
       <c r="S28">
-        <v>0.1286621518413689</v>
+        <v>0.1294738280578478</v>
       </c>
       <c r="T28">
-        <v>1.205745273753199</v>
+        <v>1.217556151700357</v>
       </c>
       <c r="U28">
         <v>0.0503</v>
@@ -3609,7 +3609,7 @@
         </is>
       </c>
       <c r="Y28">
-        <v>19.15083832000106</v>
+        <v>18.44154801185287</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -3617,22 +3617,22 @@
     </row>
     <row r="29">
       <c r="A29">
-        <v>0.27</v>
+        <v>0.28</v>
       </c>
       <c r="B29">
-        <v>0.1033435444822289</v>
+        <v>0.1029763966018448</v>
       </c>
       <c r="C29">
-        <v>91.06319624403372</v>
+        <v>90.54397486826377</v>
       </c>
       <c r="D29">
-        <v>118.9441962440337</v>
+        <v>119.7079748682638</v>
       </c>
       <c r="E29">
-        <v>-38.35899999999999</v>
+        <v>-37.07599999999999</v>
       </c>
       <c r="F29">
-        <v>34.64100000000001</v>
+        <v>35.92400000000001</v>
       </c>
       <c r="G29">
         <v>6.76</v>
@@ -3653,28 +3653,28 @@
         <v>32.13333333333334</v>
       </c>
       <c r="M29">
-        <v>1.7424423</v>
+        <v>1.8069772</v>
       </c>
       <c r="N29">
-        <v>30.39089103333334</v>
+        <v>30.32635613333334</v>
       </c>
       <c r="O29">
-        <v>10.63681186166667</v>
+        <v>10.61422464666667</v>
       </c>
       <c r="P29">
-        <v>19.75407917166667</v>
+        <v>19.71213148666667</v>
       </c>
       <c r="Q29">
-        <v>40.45407917166667</v>
+        <v>40.41213148666667</v>
       </c>
       <c r="R29">
-        <v>0.3698630136986302</v>
+        <v>0.388888888888889</v>
       </c>
       <c r="S29">
-        <v>0.1294738280578478</v>
+        <v>0.1303080508358955</v>
       </c>
       <c r="T29">
-        <v>1.217556151700357</v>
+        <v>1.229695109590492</v>
       </c>
       <c r="U29">
         <v>0.0503</v>
@@ -3691,7 +3691,7 @@
         </is>
       </c>
       <c r="Y29">
-        <v>18.44154801185287</v>
+        <v>17.78292129714384</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -3699,22 +3699,22 @@
     </row>
     <row r="30">
       <c r="A30">
-        <v>0.28</v>
+        <v>0.29</v>
       </c>
       <c r="B30">
-        <v>0.1029763966018448</v>
+        <v>0.1026092487214607</v>
       </c>
       <c r="C30">
-        <v>90.54397486826377</v>
+        <v>90.03462581819004</v>
       </c>
       <c r="D30">
-        <v>119.7079748682638</v>
+        <v>120.48162581819</v>
       </c>
       <c r="E30">
-        <v>-37.07599999999999</v>
+        <v>-35.79299999999999</v>
       </c>
       <c r="F30">
-        <v>35.92400000000001</v>
+        <v>37.20700000000001</v>
       </c>
       <c r="G30">
         <v>6.76</v>
@@ -3735,28 +3735,28 @@
         <v>32.13333333333334</v>
       </c>
       <c r="M30">
-        <v>1.8069772</v>
+        <v>1.8715121</v>
       </c>
       <c r="N30">
-        <v>30.32635613333334</v>
+        <v>30.26182123333334</v>
       </c>
       <c r="O30">
-        <v>10.61422464666667</v>
+        <v>10.59163743166667</v>
       </c>
       <c r="P30">
-        <v>19.71213148666667</v>
+        <v>19.67018380166667</v>
       </c>
       <c r="Q30">
-        <v>40.41213148666667</v>
+        <v>40.37018380166667</v>
       </c>
       <c r="R30">
-        <v>0.388888888888889</v>
+        <v>0.4084507042253522</v>
       </c>
       <c r="S30">
-        <v>0.1303080508358955</v>
+        <v>0.1311657728471277</v>
       </c>
       <c r="T30">
-        <v>1.229695109590492</v>
+        <v>1.242176009956405</v>
       </c>
       <c r="U30">
         <v>0.0503</v>
@@ -3773,7 +3773,7 @@
         </is>
       </c>
       <c r="Y30">
-        <v>17.78292129714384</v>
+        <v>17.1697171144837</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -3781,22 +3781,22 @@
     </row>
     <row r="31">
       <c r="A31">
-        <v>0.29</v>
+        <v>0.3</v>
       </c>
       <c r="B31">
-        <v>0.1026092487214607</v>
+        <v>0.1022421008410766</v>
       </c>
       <c r="C31">
-        <v>90.03462581819005</v>
+        <v>89.53534174805824</v>
       </c>
       <c r="D31">
-        <v>120.48162581819</v>
+        <v>121.2653417480583</v>
       </c>
       <c r="E31">
-        <v>-35.793</v>
+        <v>-34.51</v>
       </c>
       <c r="F31">
-        <v>37.207</v>
+        <v>38.49</v>
       </c>
       <c r="G31">
         <v>6.76</v>
@@ -3817,28 +3817,28 @@
         <v>32.13333333333334</v>
       </c>
       <c r="M31">
-        <v>1.8715121</v>
+        <v>1.936047</v>
       </c>
       <c r="N31">
-        <v>30.26182123333334</v>
+        <v>30.19728633333334</v>
       </c>
       <c r="O31">
-        <v>10.59163743166667</v>
+        <v>10.56905021666667</v>
       </c>
       <c r="P31">
-        <v>19.67018380166667</v>
+        <v>19.62823611666667</v>
       </c>
       <c r="Q31">
-        <v>40.37018380166667</v>
+        <v>40.32823611666667</v>
       </c>
       <c r="R31">
-        <v>0.4084507042253521</v>
+        <v>0.4285714285714286</v>
       </c>
       <c r="S31">
-        <v>0.1311657728471277</v>
+        <v>0.132048001201538</v>
       </c>
       <c r="T31">
-        <v>1.242176009956405</v>
+        <v>1.255013507475631</v>
       </c>
       <c r="U31">
         <v>0.0503</v>
@@ -3855,7 +3855,7 @@
         </is>
       </c>
       <c r="Y31">
-        <v>17.16971711448371</v>
+        <v>16.59739321066758</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -3863,22 +3863,22 @@
     </row>
     <row r="32">
       <c r="A32">
-        <v>0.3</v>
+        <v>0.31</v>
       </c>
       <c r="B32">
-        <v>0.1022421008410766</v>
+        <v>0.1018749529606925</v>
       </c>
       <c r="C32">
-        <v>89.53534174805824</v>
+        <v>89.04632035768918</v>
       </c>
       <c r="D32">
-        <v>121.2653417480583</v>
+        <v>122.0593203576892</v>
       </c>
       <c r="E32">
-        <v>-34.51</v>
+        <v>-33.227</v>
       </c>
       <c r="F32">
-        <v>38.49</v>
+        <v>39.773</v>
       </c>
       <c r="G32">
         <v>6.76</v>
@@ -3899,28 +3899,28 @@
         <v>32.13333333333334</v>
       </c>
       <c r="M32">
-        <v>1.936047</v>
+        <v>2.0005819</v>
       </c>
       <c r="N32">
-        <v>30.19728633333334</v>
+        <v>30.13275143333334</v>
       </c>
       <c r="O32">
-        <v>10.56905021666667</v>
+        <v>10.54646300166667</v>
       </c>
       <c r="P32">
-        <v>19.62823611666667</v>
+        <v>19.58628843166667</v>
       </c>
       <c r="Q32">
-        <v>40.32823611666667</v>
+        <v>40.28628843166668</v>
       </c>
       <c r="R32">
-        <v>0.4285714285714286</v>
+        <v>0.4492753623188406</v>
       </c>
       <c r="S32">
-        <v>0.132048001201538</v>
+        <v>0.132955801392308</v>
       </c>
       <c r="T32">
-        <v>1.255013507475631</v>
+        <v>1.268223106372225</v>
       </c>
       <c r="U32">
         <v>0.0503</v>
@@ -3937,7 +3937,7 @@
         </is>
       </c>
       <c r="Y32">
-        <v>16.59739321066758</v>
+        <v>16.0619934296783</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -3945,22 +3945,22 @@
     </row>
     <row r="33">
       <c r="A33">
-        <v>0.31</v>
+        <v>0.32</v>
       </c>
       <c r="B33">
-        <v>0.1018749529606925</v>
+        <v>0.1015078050803084</v>
       </c>
       <c r="C33">
-        <v>89.04632035768918</v>
+        <v>88.56776455874589</v>
       </c>
       <c r="D33">
-        <v>122.0593203576892</v>
+        <v>122.8637645587459</v>
       </c>
       <c r="E33">
-        <v>-33.227</v>
+        <v>-31.944</v>
       </c>
       <c r="F33">
-        <v>39.773</v>
+        <v>41.056</v>
       </c>
       <c r="G33">
         <v>6.76</v>
@@ -3981,28 +3981,28 @@
         <v>32.13333333333334</v>
       </c>
       <c r="M33">
-        <v>2.0005819</v>
+        <v>2.0651168</v>
       </c>
       <c r="N33">
-        <v>30.13275143333334</v>
+        <v>30.06821653333334</v>
       </c>
       <c r="O33">
-        <v>10.54646300166667</v>
+        <v>10.52387578666667</v>
       </c>
       <c r="P33">
-        <v>19.58628843166667</v>
+        <v>19.54434074666667</v>
       </c>
       <c r="Q33">
-        <v>40.28628843166668</v>
+        <v>40.24434074666667</v>
       </c>
       <c r="R33">
-        <v>0.4492753623188406</v>
+        <v>0.4705882352941177</v>
       </c>
       <c r="S33">
-        <v>0.132955801392308</v>
+        <v>0.1338903015886888</v>
       </c>
       <c r="T33">
-        <v>1.268223106372225</v>
+        <v>1.281821222883424</v>
       </c>
       <c r="U33">
         <v>0.0503</v>
@@ -4019,7 +4019,7 @@
         </is>
       </c>
       <c r="Y33">
-        <v>16.0619934296783</v>
+        <v>15.56005613500086</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4027,22 +4027,22 @@
     </row>
     <row r="34">
       <c r="A34">
-        <v>0.32</v>
+        <v>0.33</v>
       </c>
       <c r="B34">
-        <v>0.1015078050803084</v>
+        <v>0.1011406571999243</v>
       </c>
       <c r="C34">
-        <v>88.56776455874589</v>
+        <v>88.09988264761847</v>
       </c>
       <c r="D34">
-        <v>122.8637645587459</v>
+        <v>123.6788826476185</v>
       </c>
       <c r="E34">
-        <v>-31.944</v>
+        <v>-30.66099999999999</v>
       </c>
       <c r="F34">
-        <v>41.056</v>
+        <v>42.33900000000001</v>
       </c>
       <c r="G34">
         <v>6.76</v>
@@ -4063,28 +4063,28 @@
         <v>32.13333333333334</v>
       </c>
       <c r="M34">
-        <v>2.0651168</v>
+        <v>2.1296517</v>
       </c>
       <c r="N34">
-        <v>30.06821653333334</v>
+        <v>30.00368163333334</v>
       </c>
       <c r="O34">
-        <v>10.52387578666667</v>
+        <v>10.50128857166667</v>
       </c>
       <c r="P34">
-        <v>19.54434074666667</v>
+        <v>19.50239306166667</v>
       </c>
       <c r="Q34">
-        <v>40.24434074666667</v>
+        <v>40.20239306166667</v>
       </c>
       <c r="R34">
-        <v>0.4705882352941177</v>
+        <v>0.4925373134328359</v>
       </c>
       <c r="S34">
-        <v>0.1338903015886888</v>
+        <v>0.1348526973133198</v>
       </c>
       <c r="T34">
-        <v>1.281821222883424</v>
+        <v>1.295825253320331</v>
       </c>
       <c r="U34">
         <v>0.0503</v>
@@ -4101,7 +4101,7 @@
         </is>
       </c>
       <c r="Y34">
-        <v>15.56005613500086</v>
+        <v>15.08853928242507</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4109,22 +4109,22 @@
     </row>
     <row r="35">
       <c r="A35">
-        <v>0.33</v>
+        <v>0.34</v>
       </c>
       <c r="B35">
-        <v>0.1011406571999243</v>
+        <v>0.1007735093195402</v>
       </c>
       <c r="C35">
-        <v>88.09988264761847</v>
+        <v>87.64288848523753</v>
       </c>
       <c r="D35">
-        <v>123.6788826476185</v>
+        <v>124.5048884852375</v>
       </c>
       <c r="E35">
-        <v>-30.66099999999999</v>
+        <v>-29.37799999999999</v>
       </c>
       <c r="F35">
-        <v>42.33900000000001</v>
+        <v>43.62200000000001</v>
       </c>
       <c r="G35">
         <v>6.76</v>
@@ -4145,28 +4145,28 @@
         <v>32.13333333333334</v>
       </c>
       <c r="M35">
-        <v>2.1296517</v>
+        <v>2.1941866</v>
       </c>
       <c r="N35">
-        <v>30.00368163333334</v>
+        <v>29.93914673333334</v>
       </c>
       <c r="O35">
-        <v>10.50128857166667</v>
+        <v>10.47870135666667</v>
       </c>
       <c r="P35">
-        <v>19.50239306166667</v>
+        <v>19.46044537666667</v>
       </c>
       <c r="Q35">
-        <v>40.20239306166667</v>
+        <v>40.16044537666667</v>
       </c>
       <c r="R35">
-        <v>0.4925373134328359</v>
+        <v>0.5151515151515152</v>
       </c>
       <c r="S35">
-        <v>0.1348526973133198</v>
+        <v>0.1358442565447579</v>
       </c>
       <c r="T35">
-        <v>1.295825253320331</v>
+        <v>1.310253648315933</v>
       </c>
       <c r="U35">
         <v>0.0503</v>
@@ -4183,7 +4183,7 @@
         </is>
       </c>
       <c r="Y35">
-        <v>15.08853928242507</v>
+        <v>14.64475871529492</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4191,22 +4191,22 @@
     </row>
     <row r="36">
       <c r="A36">
-        <v>0.34</v>
+        <v>0.35</v>
       </c>
       <c r="B36">
-        <v>0.1007735093195402</v>
+        <v>0.1004063614391561</v>
       </c>
       <c r="C36">
-        <v>87.64288848523753</v>
+        <v>87.19700168414101</v>
       </c>
       <c r="D36">
-        <v>124.5048884852375</v>
+        <v>125.342001684141</v>
       </c>
       <c r="E36">
-        <v>-29.37799999999999</v>
+        <v>-28.09499999999999</v>
       </c>
       <c r="F36">
-        <v>43.62200000000001</v>
+        <v>44.90500000000001</v>
       </c>
       <c r="G36">
         <v>6.76</v>
@@ -4227,28 +4227,28 @@
         <v>32.13333333333334</v>
       </c>
       <c r="M36">
-        <v>2.1941866</v>
+        <v>2.2587215</v>
       </c>
       <c r="N36">
-        <v>29.93914673333334</v>
+        <v>29.87461183333334</v>
       </c>
       <c r="O36">
-        <v>10.47870135666667</v>
+        <v>10.45611414166667</v>
       </c>
       <c r="P36">
-        <v>19.46044537666667</v>
+        <v>19.41849769166667</v>
       </c>
       <c r="Q36">
-        <v>40.16044537666667</v>
+        <v>40.11849769166668</v>
       </c>
       <c r="R36">
-        <v>0.5151515151515152</v>
+        <v>0.5384615384615385</v>
       </c>
       <c r="S36">
-        <v>0.1358442565447579</v>
+        <v>0.1368663252910094</v>
       </c>
       <c r="T36">
-        <v>1.310253648315933</v>
+        <v>1.325125993926783</v>
       </c>
       <c r="U36">
         <v>0.0503</v>
@@ -4265,7 +4265,7 @@
         </is>
       </c>
       <c r="Y36">
-        <v>14.64475871529492</v>
+        <v>14.22633703771507</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4273,22 +4273,22 @@
     </row>
     <row r="37">
       <c r="A37">
-        <v>0.35</v>
+        <v>0.36</v>
       </c>
       <c r="B37">
-        <v>0.1004063614391561</v>
+        <v>0.100039213558772</v>
       </c>
       <c r="C37">
-        <v>87.19700168414101</v>
+        <v>86.76244780313883</v>
       </c>
       <c r="D37">
-        <v>125.342001684141</v>
+        <v>126.1904478031389</v>
       </c>
       <c r="E37">
-        <v>-28.09499999999999</v>
+        <v>-26.81199999999999</v>
       </c>
       <c r="F37">
-        <v>44.90500000000001</v>
+        <v>46.18800000000001</v>
       </c>
       <c r="G37">
         <v>6.76</v>
@@ -4309,28 +4309,28 @@
         <v>32.13333333333334</v>
       </c>
       <c r="M37">
-        <v>2.2587215</v>
+        <v>2.3232564</v>
       </c>
       <c r="N37">
-        <v>29.87461183333334</v>
+        <v>29.81007693333334</v>
       </c>
       <c r="O37">
-        <v>10.45611414166667</v>
+        <v>10.43352692666667</v>
       </c>
       <c r="P37">
-        <v>19.41849769166667</v>
+        <v>19.37655000666667</v>
       </c>
       <c r="Q37">
-        <v>40.11849769166668</v>
+        <v>40.07655000666666</v>
       </c>
       <c r="R37">
-        <v>0.5384615384615385</v>
+        <v>0.5625000000000001</v>
       </c>
       <c r="S37">
-        <v>0.1368663252910094</v>
+        <v>0.1379203336855813</v>
       </c>
       <c r="T37">
-        <v>1.325125993926783</v>
+        <v>1.340463100337973</v>
       </c>
       <c r="U37">
         <v>0.0503</v>
@@ -4347,7 +4347,7 @@
         </is>
       </c>
       <c r="Y37">
-        <v>14.22633703771507</v>
+        <v>13.83116100888965</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4355,22 +4355,22 @@
     </row>
     <row r="38">
       <c r="A38">
-        <v>0.36</v>
+        <v>0.37</v>
       </c>
       <c r="B38">
-        <v>0.100039213558772</v>
+        <v>0.09967206567838791</v>
       </c>
       <c r="C38">
-        <v>86.76244780313881</v>
+        <v>86.33945854993721</v>
       </c>
       <c r="D38">
-        <v>126.1904478031388</v>
+        <v>127.0504585499372</v>
       </c>
       <c r="E38">
-        <v>-26.812</v>
+        <v>-25.529</v>
       </c>
       <c r="F38">
-        <v>46.188</v>
+        <v>47.471</v>
       </c>
       <c r="G38">
         <v>6.76</v>
@@ -4391,28 +4391,28 @@
         <v>32.13333333333334</v>
       </c>
       <c r="M38">
-        <v>2.3232564</v>
+        <v>2.3877913</v>
       </c>
       <c r="N38">
-        <v>29.81007693333334</v>
+        <v>29.74554203333334</v>
       </c>
       <c r="O38">
-        <v>10.43352692666667</v>
+        <v>10.41093971166667</v>
       </c>
       <c r="P38">
-        <v>19.37655000666667</v>
+        <v>19.33460232166667</v>
       </c>
       <c r="Q38">
-        <v>40.07655000666667</v>
+        <v>40.03460232166667</v>
       </c>
       <c r="R38">
-        <v>0.5625</v>
+        <v>0.5873015873015873</v>
       </c>
       <c r="S38">
-        <v>0.1379203336855813</v>
+        <v>0.1390078026641078</v>
       </c>
       <c r="T38">
-        <v>1.340463100337973</v>
+        <v>1.356287099016184</v>
       </c>
       <c r="U38">
         <v>0.0503</v>
@@ -4429,7 +4429,7 @@
         </is>
       </c>
       <c r="Y38">
-        <v>13.83116100888965</v>
+        <v>13.45734584648723</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4437,22 +4437,22 @@
     </row>
     <row r="39">
       <c r="A39">
-        <v>0.37</v>
+        <v>0.38</v>
       </c>
       <c r="B39">
-        <v>0.09967206567838791</v>
+        <v>0.09930491779800379</v>
       </c>
       <c r="C39">
-        <v>86.33945854993721</v>
+        <v>85.92827199210602</v>
       </c>
       <c r="D39">
-        <v>127.0504585499372</v>
+        <v>127.922271992106</v>
       </c>
       <c r="E39">
-        <v>-25.529</v>
+        <v>-24.246</v>
       </c>
       <c r="F39">
-        <v>47.471</v>
+        <v>48.754</v>
       </c>
       <c r="G39">
         <v>6.76</v>
@@ -4473,28 +4473,28 @@
         <v>32.13333333333334</v>
       </c>
       <c r="M39">
-        <v>2.3877913</v>
+        <v>2.4523262</v>
       </c>
       <c r="N39">
-        <v>29.74554203333334</v>
+        <v>29.68100713333334</v>
       </c>
       <c r="O39">
-        <v>10.41093971166667</v>
+        <v>10.38835249666667</v>
       </c>
       <c r="P39">
-        <v>19.33460232166667</v>
+        <v>19.29265463666667</v>
       </c>
       <c r="Q39">
-        <v>40.03460232166667</v>
+        <v>39.99265463666667</v>
       </c>
       <c r="R39">
-        <v>0.5873015873015873</v>
+        <v>0.6129032258064516</v>
       </c>
       <c r="S39">
-        <v>0.1390078026641078</v>
+        <v>0.1401303512871029</v>
       </c>
       <c r="T39">
-        <v>1.356287099016184</v>
+        <v>1.372621549264661</v>
       </c>
       <c r="U39">
         <v>0.0503</v>
@@ -4511,7 +4511,7 @@
         </is>
       </c>
       <c r="Y39">
-        <v>13.45734584648723</v>
+        <v>13.10320516631651</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4519,22 +4519,22 @@
     </row>
     <row r="40">
       <c r="A40">
-        <v>0.38</v>
+        <v>0.39</v>
       </c>
       <c r="B40">
-        <v>0.09930491779800379</v>
+        <v>0.09931801991761971</v>
       </c>
       <c r="C40">
-        <v>85.92827199210602</v>
+        <v>84.61395444874847</v>
       </c>
       <c r="D40">
-        <v>127.922271992106</v>
+        <v>127.8909544487485</v>
       </c>
       <c r="E40">
-        <v>-24.246</v>
+        <v>-22.96299999999999</v>
       </c>
       <c r="F40">
-        <v>48.754</v>
+        <v>50.03700000000001</v>
       </c>
       <c r="G40">
         <v>6.76</v>
@@ -4555,45 +4555,45 @@
         <v>32.13333333333334</v>
       </c>
       <c r="M40">
-        <v>2.4523262</v>
+        <v>2.5919166</v>
       </c>
       <c r="N40">
-        <v>29.68100713333334</v>
+        <v>29.54141673333334</v>
       </c>
       <c r="O40">
-        <v>10.38835249666667</v>
+        <v>10.33949585666667</v>
       </c>
       <c r="P40">
-        <v>19.29265463666667</v>
+        <v>19.20192087666667</v>
       </c>
       <c r="Q40">
-        <v>39.99265463666667</v>
+        <v>39.90192087666667</v>
       </c>
       <c r="R40">
-        <v>0.6129032258064516</v>
+        <v>0.639344262295082</v>
       </c>
       <c r="S40">
-        <v>0.1401303512871029</v>
+        <v>0.1412897047829831</v>
       </c>
       <c r="T40">
-        <v>1.372621549264661</v>
+        <v>1.389491555258989</v>
       </c>
       <c r="U40">
-        <v>0.0503</v>
+        <v>0.0518</v>
       </c>
       <c r="V40">
         <v>0.35</v>
       </c>
       <c r="W40">
-        <v>0.032695</v>
+        <v>0.03367</v>
       </c>
       <c r="X40" t="inlineStr">
         <is>
-          <t>Aaa/AAA</t>
+          <t>Aa2/AA</t>
         </is>
       </c>
       <c r="Y40">
-        <v>13.10320516631651</v>
+        <v>12.39751824319245</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4601,22 +4601,22 @@
     </row>
     <row r="41">
       <c r="A41">
-        <v>0.39</v>
+        <v>0.4</v>
       </c>
       <c r="B41">
-        <v>0.09931801991761971</v>
+        <v>0.0989606220372356</v>
       </c>
       <c r="C41">
-        <v>84.61395444874847</v>
+        <v>84.19076297409394</v>
       </c>
       <c r="D41">
-        <v>127.8909544487485</v>
+        <v>128.750762974094</v>
       </c>
       <c r="E41">
-        <v>-22.96299999999999</v>
+        <v>-21.67999999999999</v>
       </c>
       <c r="F41">
-        <v>50.03700000000001</v>
+        <v>51.32000000000001</v>
       </c>
       <c r="G41">
         <v>6.76</v>
@@ -4637,28 +4637,28 @@
         <v>32.13333333333334</v>
       </c>
       <c r="M41">
-        <v>2.5919166</v>
+        <v>2.658376000000001</v>
       </c>
       <c r="N41">
-        <v>29.54141673333334</v>
+        <v>29.47495733333334</v>
       </c>
       <c r="O41">
-        <v>10.33949585666667</v>
+        <v>10.31623506666667</v>
       </c>
       <c r="P41">
-        <v>19.20192087666667</v>
+        <v>19.15872226666667</v>
       </c>
       <c r="Q41">
-        <v>39.90192087666667</v>
+        <v>39.85872226666667</v>
       </c>
       <c r="R41">
-        <v>0.639344262295082</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="S41">
-        <v>0.1412897047829831</v>
+        <v>0.1424877033953927</v>
       </c>
       <c r="T41">
-        <v>1.389491555258989</v>
+        <v>1.406923894786461</v>
       </c>
       <c r="U41">
         <v>0.0518</v>
@@ -4675,7 +4675,7 @@
         </is>
       </c>
       <c r="Y41">
-        <v>12.39751824319245</v>
+        <v>12.08758028711263</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -4683,22 +4683,22 @@
     </row>
     <row r="42">
       <c r="A42">
-        <v>0.4</v>
+        <v>0.41</v>
       </c>
       <c r="B42">
-        <v>0.0989606220372356</v>
+        <v>0.09860322415685151</v>
       </c>
       <c r="C42">
-        <v>84.19076297409394</v>
+        <v>83.77921070327216</v>
       </c>
       <c r="D42">
-        <v>128.750762974094</v>
+        <v>129.6222107032722</v>
       </c>
       <c r="E42">
-        <v>-21.67999999999999</v>
+        <v>-20.39699999999999</v>
       </c>
       <c r="F42">
-        <v>51.32000000000001</v>
+        <v>52.60300000000001</v>
       </c>
       <c r="G42">
         <v>6.76</v>
@@ -4719,28 +4719,28 @@
         <v>32.13333333333334</v>
       </c>
       <c r="M42">
-        <v>2.658376000000001</v>
+        <v>2.7248354</v>
       </c>
       <c r="N42">
-        <v>29.47495733333334</v>
+        <v>29.40849793333334</v>
       </c>
       <c r="O42">
-        <v>10.31623506666667</v>
+        <v>10.29297427666667</v>
       </c>
       <c r="P42">
-        <v>19.15872226666667</v>
+        <v>19.11552365666667</v>
       </c>
       <c r="Q42">
-        <v>39.85872226666667</v>
+        <v>39.81552365666667</v>
       </c>
       <c r="R42">
-        <v>0.6666666666666667</v>
+        <v>0.6949152542372882</v>
       </c>
       <c r="S42">
-        <v>0.1424877033953927</v>
+        <v>0.1437263121302568</v>
       </c>
       <c r="T42">
-        <v>1.406923894786461</v>
+        <v>1.424947161077577</v>
       </c>
       <c r="U42">
         <v>0.0518</v>
@@ -4757,7 +4757,7 @@
         </is>
       </c>
       <c r="Y42">
-        <v>12.08758028711263</v>
+        <v>11.79276125571964</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -4765,22 +4765,22 @@
     </row>
     <row r="43">
       <c r="A43">
-        <v>0.41</v>
+        <v>0.42</v>
       </c>
       <c r="B43">
-        <v>0.09860322415685151</v>
+        <v>0.0982458262764674</v>
       </c>
       <c r="C43">
-        <v>83.77921070327216</v>
+        <v>83.37953558620642</v>
       </c>
       <c r="D43">
-        <v>129.6222107032722</v>
+        <v>130.5055355862064</v>
       </c>
       <c r="E43">
-        <v>-20.39699999999999</v>
+        <v>-19.11399999999999</v>
       </c>
       <c r="F43">
-        <v>52.60300000000001</v>
+        <v>53.88600000000001</v>
       </c>
       <c r="G43">
         <v>6.76</v>
@@ -4801,28 +4801,28 @@
         <v>32.13333333333334</v>
       </c>
       <c r="M43">
-        <v>2.7248354</v>
+        <v>2.791294800000001</v>
       </c>
       <c r="N43">
-        <v>29.40849793333334</v>
+        <v>29.34203853333334</v>
       </c>
       <c r="O43">
-        <v>10.29297427666667</v>
+        <v>10.26971348666667</v>
       </c>
       <c r="P43">
-        <v>19.11552365666667</v>
+        <v>19.07232504666667</v>
       </c>
       <c r="Q43">
-        <v>39.81552365666667</v>
+        <v>39.77232504666667</v>
       </c>
       <c r="R43">
-        <v>0.6949152542372882</v>
+        <v>0.7241379310344829</v>
       </c>
       <c r="S43">
-        <v>0.1437263121302568</v>
+        <v>0.1450076315111507</v>
       </c>
       <c r="T43">
-        <v>1.424947161077577</v>
+        <v>1.443591919309765</v>
       </c>
       <c r="U43">
         <v>0.0518</v>
@@ -4839,7 +4839,7 @@
         </is>
       </c>
       <c r="Y43">
-        <v>11.79276125571964</v>
+        <v>11.51198122582156</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -4847,22 +4847,22 @@
     </row>
     <row r="44">
       <c r="A44">
-        <v>0.42</v>
+        <v>0.43</v>
       </c>
       <c r="B44">
-        <v>0.09824582627646741</v>
+        <v>0.09788842839608332</v>
       </c>
       <c r="C44">
-        <v>83.3795355862064</v>
+        <v>82.99198210346793</v>
       </c>
       <c r="D44">
-        <v>130.5055355862064</v>
+        <v>131.400982103468</v>
       </c>
       <c r="E44">
-        <v>-19.114</v>
+        <v>-17.831</v>
       </c>
       <c r="F44">
-        <v>53.886</v>
+        <v>55.169</v>
       </c>
       <c r="G44">
         <v>6.76</v>
@@ -4883,28 +4883,28 @@
         <v>32.13333333333334</v>
       </c>
       <c r="M44">
-        <v>2.7912948</v>
+        <v>2.8577542</v>
       </c>
       <c r="N44">
-        <v>29.34203853333334</v>
+        <v>29.27557913333334</v>
       </c>
       <c r="O44">
-        <v>10.26971348666667</v>
+        <v>10.24645269666667</v>
       </c>
       <c r="P44">
-        <v>19.07232504666667</v>
+        <v>19.02912643666667</v>
       </c>
       <c r="Q44">
-        <v>39.77232504666667</v>
+        <v>39.72912643666668</v>
       </c>
       <c r="R44">
-        <v>0.7241379310344827</v>
+        <v>0.7543859649122806</v>
       </c>
       <c r="S44">
-        <v>0.1450076315111507</v>
+        <v>0.1463339094668128</v>
       </c>
       <c r="T44">
-        <v>1.443591919309765</v>
+        <v>1.462890879585188</v>
       </c>
       <c r="U44">
         <v>0.0518</v>
@@ -4921,7 +4921,7 @@
         </is>
       </c>
       <c r="Y44">
-        <v>11.51198122582156</v>
+        <v>11.2442607321978</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -4929,22 +4929,22 @@
     </row>
     <row r="45">
       <c r="A45">
-        <v>0.43</v>
+        <v>0.44</v>
       </c>
       <c r="B45">
-        <v>0.09788842839608332</v>
+        <v>0.09753103051569921</v>
       </c>
       <c r="C45">
-        <v>82.99198210346793</v>
+        <v>82.61680149187001</v>
       </c>
       <c r="D45">
-        <v>131.400982103468</v>
+        <v>132.30880149187</v>
       </c>
       <c r="E45">
-        <v>-17.831</v>
+        <v>-16.54799999999999</v>
       </c>
       <c r="F45">
-        <v>55.169</v>
+        <v>56.45200000000001</v>
       </c>
       <c r="G45">
         <v>6.76</v>
@@ -4965,28 +4965,28 @@
         <v>32.13333333333334</v>
       </c>
       <c r="M45">
-        <v>2.8577542</v>
+        <v>2.9242136</v>
       </c>
       <c r="N45">
-        <v>29.27557913333334</v>
+        <v>29.20911973333334</v>
       </c>
       <c r="O45">
-        <v>10.24645269666667</v>
+        <v>10.22319190666667</v>
       </c>
       <c r="P45">
-        <v>19.02912643666667</v>
+        <v>18.98592782666667</v>
       </c>
       <c r="Q45">
-        <v>39.72912643666668</v>
+        <v>39.68592782666667</v>
       </c>
       <c r="R45">
-        <v>0.7543859649122806</v>
+        <v>0.7857142857142857</v>
       </c>
       <c r="S45">
-        <v>0.1463339094668128</v>
+        <v>0.14770755449232</v>
       </c>
       <c r="T45">
-        <v>1.462890879585188</v>
+        <v>1.482879088441876</v>
       </c>
       <c r="U45">
         <v>0.0518</v>
@@ -5003,7 +5003,7 @@
         </is>
       </c>
       <c r="Y45">
-        <v>11.2442607321978</v>
+        <v>10.98870935192058</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5011,22 +5011,22 @@
     </row>
     <row r="46">
       <c r="A46">
-        <v>0.44</v>
+        <v>0.45</v>
       </c>
       <c r="B46">
-        <v>0.09753103051569921</v>
+        <v>0.09717363263531512</v>
       </c>
       <c r="C46">
-        <v>82.61680149187001</v>
+        <v>82.25425197947769</v>
       </c>
       <c r="D46">
-        <v>132.30880149187</v>
+        <v>133.2292519794777</v>
       </c>
       <c r="E46">
-        <v>-16.54799999999999</v>
+        <v>-15.26499999999999</v>
       </c>
       <c r="F46">
-        <v>56.45200000000001</v>
+        <v>57.73500000000001</v>
       </c>
       <c r="G46">
         <v>6.76</v>
@@ -5047,28 +5047,28 @@
         <v>32.13333333333334</v>
       </c>
       <c r="M46">
-        <v>2.9242136</v>
+        <v>2.990673</v>
       </c>
       <c r="N46">
-        <v>29.20911973333334</v>
+        <v>29.14266033333334</v>
       </c>
       <c r="O46">
-        <v>10.22319190666667</v>
+        <v>10.19993111666667</v>
       </c>
       <c r="P46">
-        <v>18.98592782666667</v>
+        <v>18.94272921666667</v>
       </c>
       <c r="Q46">
-        <v>39.68592782666667</v>
+        <v>39.64272921666667</v>
       </c>
       <c r="R46">
-        <v>0.7857142857142857</v>
+        <v>0.8181818181818181</v>
       </c>
       <c r="S46">
-        <v>0.14770755449232</v>
+        <v>0.1491311502460275</v>
       </c>
       <c r="T46">
-        <v>1.482879088441876</v>
+        <v>1.50359414125699</v>
       </c>
       <c r="U46">
         <v>0.0518</v>
@@ -5085,7 +5085,7 @@
         </is>
       </c>
       <c r="Y46">
-        <v>10.98870935192058</v>
+        <v>10.74451581076679</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5093,22 +5093,22 @@
     </row>
     <row r="47">
       <c r="A47">
-        <v>0.45</v>
+        <v>0.46</v>
       </c>
       <c r="B47">
-        <v>0.09717363263531512</v>
+        <v>0.09681623475493104</v>
       </c>
       <c r="C47">
-        <v>82.25425197947769</v>
+        <v>81.904599030497</v>
       </c>
       <c r="D47">
-        <v>133.2292519794777</v>
+        <v>134.162599030497</v>
       </c>
       <c r="E47">
-        <v>-15.26499999999999</v>
+        <v>-13.98199999999999</v>
       </c>
       <c r="F47">
-        <v>57.73500000000001</v>
+        <v>59.01800000000001</v>
       </c>
       <c r="G47">
         <v>6.76</v>
@@ -5129,28 +5129,28 @@
         <v>32.13333333333334</v>
       </c>
       <c r="M47">
-        <v>2.990673</v>
+        <v>3.0571324</v>
       </c>
       <c r="N47">
-        <v>29.14266033333334</v>
+        <v>29.07620093333334</v>
       </c>
       <c r="O47">
-        <v>10.19993111666667</v>
+        <v>10.17667032666667</v>
       </c>
       <c r="P47">
-        <v>18.94272921666667</v>
+        <v>18.89953060666667</v>
       </c>
       <c r="Q47">
-        <v>39.64272921666667</v>
+        <v>39.59953060666668</v>
       </c>
       <c r="R47">
-        <v>0.8181818181818181</v>
+        <v>0.8518518518518519</v>
       </c>
       <c r="S47">
-        <v>0.1491311502460275</v>
+        <v>0.1506074717683908</v>
       </c>
       <c r="T47">
-        <v>1.50359414125699</v>
+        <v>1.525076418250441</v>
       </c>
       <c r="U47">
         <v>0.0518</v>
@@ -5167,7 +5167,7 @@
         </is>
       </c>
       <c r="Y47">
-        <v>10.74451581076679</v>
+        <v>10.51093938009794</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5175,22 +5175,22 @@
     </row>
     <row r="48">
       <c r="A48">
-        <v>0.46</v>
+        <v>0.47</v>
       </c>
       <c r="B48">
-        <v>0.09681623475493104</v>
+        <v>0.09645883687454691</v>
       </c>
       <c r="C48">
-        <v>81.904599030497</v>
+        <v>81.56811560052932</v>
       </c>
       <c r="D48">
-        <v>134.162599030497</v>
+        <v>135.1091156005293</v>
       </c>
       <c r="E48">
-        <v>-13.98199999999999</v>
+        <v>-12.69899999999999</v>
       </c>
       <c r="F48">
-        <v>59.01800000000001</v>
+        <v>60.30100000000001</v>
       </c>
       <c r="G48">
         <v>6.76</v>
@@ -5211,28 +5211,28 @@
         <v>32.13333333333334</v>
       </c>
       <c r="M48">
-        <v>3.0571324</v>
+        <v>3.1235918</v>
       </c>
       <c r="N48">
-        <v>29.07620093333334</v>
+        <v>29.00974153333334</v>
       </c>
       <c r="O48">
-        <v>10.17667032666667</v>
+        <v>10.15340953666667</v>
       </c>
       <c r="P48">
-        <v>18.89953060666667</v>
+        <v>18.85633199666667</v>
       </c>
       <c r="Q48">
-        <v>39.59953060666668</v>
+        <v>39.55633199666667</v>
       </c>
       <c r="R48">
-        <v>0.8518518518518519</v>
+        <v>0.8867924528301887</v>
       </c>
       <c r="S48">
-        <v>0.1506074717683908</v>
+        <v>0.152139503536881</v>
       </c>
       <c r="T48">
-        <v>1.525076418250441</v>
+        <v>1.547369347205908</v>
       </c>
       <c r="U48">
         <v>0.0518</v>
@@ -5249,7 +5249,7 @@
         </is>
       </c>
       <c r="Y48">
-        <v>10.51093938009794</v>
+        <v>10.28730237201075</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5257,22 +5257,22 @@
     </row>
     <row r="49">
       <c r="A49">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="B49">
-        <v>0.09645883687454691</v>
+        <v>0.09610143899416282</v>
       </c>
       <c r="C49">
-        <v>81.56811560052932</v>
+        <v>81.24508240270771</v>
       </c>
       <c r="D49">
-        <v>135.1091156005293</v>
+        <v>136.0690824027077</v>
       </c>
       <c r="E49">
-        <v>-12.69899999999999</v>
+        <v>-11.41599999999999</v>
       </c>
       <c r="F49">
-        <v>60.30100000000001</v>
+        <v>61.58400000000001</v>
       </c>
       <c r="G49">
         <v>6.76</v>
@@ -5293,28 +5293,28 @@
         <v>32.13333333333334</v>
       </c>
       <c r="M49">
-        <v>3.1235918</v>
+        <v>3.190051200000001</v>
       </c>
       <c r="N49">
-        <v>29.00974153333334</v>
+        <v>28.94328213333334</v>
       </c>
       <c r="O49">
-        <v>10.15340953666667</v>
+        <v>10.13014874666667</v>
       </c>
       <c r="P49">
-        <v>18.85633199666667</v>
+        <v>18.81313338666667</v>
       </c>
       <c r="Q49">
-        <v>39.55633199666667</v>
+        <v>39.51313338666667</v>
       </c>
       <c r="R49">
-        <v>0.8867924528301887</v>
+        <v>0.9230769230769231</v>
       </c>
       <c r="S49">
-        <v>0.152139503536881</v>
+        <v>0.1537304596041593</v>
       </c>
       <c r="T49">
-        <v>1.547369347205908</v>
+        <v>1.570519696505817</v>
       </c>
       <c r="U49">
         <v>0.0518</v>
@@ -5331,7 +5331,7 @@
         </is>
       </c>
       <c r="Y49">
-        <v>10.28730237201075</v>
+        <v>10.07298357259386</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5339,22 +5339,22 @@
     </row>
     <row r="50">
       <c r="A50">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="B50">
-        <v>0.09610143899416282</v>
+        <v>0.09574404111377871</v>
       </c>
       <c r="C50">
-        <v>81.24508240270771</v>
+        <v>80.93578818526048</v>
       </c>
       <c r="D50">
-        <v>136.0690824027077</v>
+        <v>137.0427881852605</v>
       </c>
       <c r="E50">
-        <v>-11.416</v>
+        <v>-10.133</v>
       </c>
       <c r="F50">
-        <v>61.584</v>
+        <v>62.867</v>
       </c>
       <c r="G50">
         <v>6.76</v>
@@ -5375,28 +5375,28 @@
         <v>32.13333333333334</v>
       </c>
       <c r="M50">
-        <v>3.1900512</v>
+        <v>3.2565106</v>
       </c>
       <c r="N50">
-        <v>28.94328213333334</v>
+        <v>28.87682273333334</v>
       </c>
       <c r="O50">
-        <v>10.13014874666667</v>
+        <v>10.10688795666667</v>
       </c>
       <c r="P50">
-        <v>18.81313338666667</v>
+        <v>18.76993477666667</v>
       </c>
       <c r="Q50">
-        <v>39.51313338666667</v>
+        <v>39.46993477666668</v>
       </c>
       <c r="R50">
-        <v>0.923076923076923</v>
+        <v>0.9607843137254901</v>
       </c>
       <c r="S50">
-        <v>0.1537304596041593</v>
+        <v>0.1553838061054485</v>
       </c>
       <c r="T50">
-        <v>1.570519696505817</v>
+        <v>1.594577902641017</v>
       </c>
       <c r="U50">
         <v>0.0518</v>
@@ -5413,7 +5413,7 @@
         </is>
       </c>
       <c r="Y50">
-        <v>10.07298357259386</v>
+        <v>9.86741247927562</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5421,22 +5421,22 @@
     </row>
     <row r="51">
       <c r="A51">
-        <v>0.49</v>
+        <v>0.5</v>
       </c>
       <c r="B51">
-        <v>0.09574404111377871</v>
+        <v>0.09593914323339461</v>
       </c>
       <c r="C51">
-        <v>80.93578818526048</v>
+        <v>79.11952541432407</v>
       </c>
       <c r="D51">
-        <v>137.0427881852605</v>
+        <v>136.5095254143241</v>
       </c>
       <c r="E51">
-        <v>-10.133</v>
+        <v>-8.849999999999994</v>
       </c>
       <c r="F51">
-        <v>62.867</v>
+        <v>64.15000000000001</v>
       </c>
       <c r="G51">
         <v>6.76</v>
@@ -5457,45 +5457,45 @@
         <v>32.13333333333334</v>
       </c>
       <c r="M51">
-        <v>3.2565106</v>
+        <v>3.432025</v>
       </c>
       <c r="N51">
-        <v>28.87682273333334</v>
+        <v>28.70130833333334</v>
       </c>
       <c r="O51">
-        <v>10.10688795666667</v>
+        <v>10.04545791666667</v>
       </c>
       <c r="P51">
-        <v>18.76993477666667</v>
+        <v>18.65585041666667</v>
       </c>
       <c r="Q51">
-        <v>39.46993477666668</v>
+        <v>39.35585041666667</v>
       </c>
       <c r="R51">
-        <v>0.9607843137254901</v>
+        <v>1</v>
       </c>
       <c r="S51">
-        <v>0.1553838061054485</v>
+        <v>0.1571032864667892</v>
       </c>
       <c r="T51">
-        <v>1.594577902641017</v>
+        <v>1.619598437021624</v>
       </c>
       <c r="U51">
-        <v>0.0518</v>
+        <v>0.0535</v>
       </c>
       <c r="V51">
         <v>0.35</v>
       </c>
       <c r="W51">
-        <v>0.03367</v>
+        <v>0.034775</v>
       </c>
       <c r="X51" t="inlineStr">
         <is>
-          <t>Aa2/AA</t>
+          <t>A1/A+</t>
         </is>
       </c>
       <c r="Y51">
-        <v>9.86741247927562</v>
+        <v>9.362791160709302</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5503,22 +5503,22 @@
     </row>
     <row r="52">
       <c r="A52">
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="B52">
-        <v>0.09593914323339461</v>
+        <v>0.09559279535301052</v>
       </c>
       <c r="C52">
-        <v>79.11952541432407</v>
+        <v>78.78605605313025</v>
       </c>
       <c r="D52">
-        <v>136.5095254143241</v>
+        <v>137.4590560531303</v>
       </c>
       <c r="E52">
-        <v>-8.849999999999994</v>
+        <v>-7.566999999999993</v>
       </c>
       <c r="F52">
-        <v>64.15000000000001</v>
+        <v>65.43300000000001</v>
       </c>
       <c r="G52">
         <v>6.76</v>
@@ -5539,28 +5539,28 @@
         <v>32.13333333333334</v>
       </c>
       <c r="M52">
-        <v>3.432025</v>
+        <v>3.5006655</v>
       </c>
       <c r="N52">
-        <v>28.70130833333334</v>
+        <v>28.63266783333334</v>
       </c>
       <c r="O52">
-        <v>10.04545791666667</v>
+        <v>10.02143374166667</v>
       </c>
       <c r="P52">
-        <v>18.65585041666667</v>
+        <v>18.61123409166667</v>
       </c>
       <c r="Q52">
-        <v>39.35585041666667</v>
+        <v>39.31123409166668</v>
       </c>
       <c r="R52">
-        <v>1</v>
+        <v>1.040816326530612</v>
       </c>
       <c r="S52">
-        <v>0.1571032864667892</v>
+        <v>0.1588929497000215</v>
       </c>
       <c r="T52">
-        <v>1.619598437021624</v>
+        <v>1.645640217703481</v>
       </c>
       <c r="U52">
         <v>0.0535</v>
@@ -5577,7 +5577,7 @@
         </is>
       </c>
       <c r="Y52">
-        <v>9.362791160709302</v>
+        <v>9.179207020303236</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5585,22 +5585,22 @@
     </row>
     <row r="53">
       <c r="A53">
-        <v>0.51</v>
+        <v>0.52</v>
       </c>
       <c r="B53">
-        <v>0.09559279535301052</v>
+        <v>0.09524644747262642</v>
       </c>
       <c r="C53">
-        <v>78.78605605313025</v>
+        <v>78.46588867583702</v>
       </c>
       <c r="D53">
-        <v>137.4590560531303</v>
+        <v>138.421888675837</v>
       </c>
       <c r="E53">
-        <v>-7.566999999999993</v>
+        <v>-6.283999999999992</v>
       </c>
       <c r="F53">
-        <v>65.43300000000001</v>
+        <v>66.71600000000001</v>
       </c>
       <c r="G53">
         <v>6.76</v>
@@ -5621,28 +5621,28 @@
         <v>32.13333333333334</v>
       </c>
       <c r="M53">
-        <v>3.5006655</v>
+        <v>3.569306000000001</v>
       </c>
       <c r="N53">
-        <v>28.63266783333334</v>
+        <v>28.56402733333334</v>
       </c>
       <c r="O53">
-        <v>10.02143374166667</v>
+        <v>9.997409566666668</v>
       </c>
       <c r="P53">
-        <v>18.61123409166667</v>
+        <v>18.56661776666667</v>
       </c>
       <c r="Q53">
-        <v>39.31123409166668</v>
+        <v>39.26661776666667</v>
       </c>
       <c r="R53">
-        <v>1.040816326530612</v>
+        <v>1.083333333333333</v>
       </c>
       <c r="S53">
-        <v>0.1588929497000215</v>
+        <v>0.1607571822346384</v>
       </c>
       <c r="T53">
-        <v>1.645640217703481</v>
+        <v>1.672767072580415</v>
       </c>
       <c r="U53">
         <v>0.0535</v>
@@ -5659,7 +5659,7 @@
         </is>
       </c>
       <c r="Y53">
-        <v>9.179207020303236</v>
+        <v>9.002683808374327</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -5667,22 +5667,22 @@
     </row>
     <row r="54">
       <c r="A54">
-        <v>0.52</v>
+        <v>0.53</v>
       </c>
       <c r="B54">
-        <v>0.09524644747262642</v>
+        <v>0.09490009959224233</v>
       </c>
       <c r="C54">
-        <v>78.46588867583702</v>
+        <v>78.15930477559606</v>
       </c>
       <c r="D54">
-        <v>138.421888675837</v>
+        <v>139.3983047755961</v>
       </c>
       <c r="E54">
-        <v>-6.283999999999992</v>
+        <v>-5.000999999999991</v>
       </c>
       <c r="F54">
-        <v>66.71600000000001</v>
+        <v>67.99900000000001</v>
       </c>
       <c r="G54">
         <v>6.76</v>
@@ -5703,28 +5703,28 @@
         <v>32.13333333333334</v>
       </c>
       <c r="M54">
-        <v>3.569306000000001</v>
+        <v>3.6379465</v>
       </c>
       <c r="N54">
-        <v>28.56402733333334</v>
+        <v>28.49538683333334</v>
       </c>
       <c r="O54">
-        <v>9.997409566666668</v>
+        <v>9.973385391666667</v>
       </c>
       <c r="P54">
-        <v>18.56661776666667</v>
+        <v>18.52200144166667</v>
       </c>
       <c r="Q54">
-        <v>39.26661776666667</v>
+        <v>39.22200144166667</v>
       </c>
       <c r="R54">
-        <v>1.083333333333333</v>
+        <v>1.127659574468085</v>
       </c>
       <c r="S54">
-        <v>0.1607571822346384</v>
+        <v>0.1627007438132816</v>
       </c>
       <c r="T54">
-        <v>1.672767072580415</v>
+        <v>1.701048261707431</v>
       </c>
       <c r="U54">
         <v>0.0535</v>
@@ -5741,7 +5741,7 @@
         </is>
       </c>
       <c r="Y54">
-        <v>9.002683808374327</v>
+        <v>8.832821849725754</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -5749,22 +5749,22 @@
     </row>
     <row r="55">
       <c r="A55">
-        <v>0.53</v>
+        <v>0.54</v>
       </c>
       <c r="B55">
-        <v>0.09490009959224233</v>
+        <v>0.09455375171185823</v>
       </c>
       <c r="C55">
-        <v>78.15930477559606</v>
+        <v>77.86659384449703</v>
       </c>
       <c r="D55">
-        <v>139.3983047755961</v>
+        <v>140.3885938444971</v>
       </c>
       <c r="E55">
-        <v>-5.000999999999991</v>
+        <v>-3.717999999999989</v>
       </c>
       <c r="F55">
-        <v>67.99900000000001</v>
+        <v>69.28200000000001</v>
       </c>
       <c r="G55">
         <v>6.76</v>
@@ -5785,28 +5785,28 @@
         <v>32.13333333333334</v>
       </c>
       <c r="M55">
-        <v>3.6379465</v>
+        <v>3.706587</v>
       </c>
       <c r="N55">
-        <v>28.49538683333334</v>
+        <v>28.42674633333334</v>
       </c>
       <c r="O55">
-        <v>9.973385391666667</v>
+        <v>9.949361216666668</v>
       </c>
       <c r="P55">
-        <v>18.52200144166667</v>
+        <v>18.47738511666667</v>
       </c>
       <c r="Q55">
-        <v>39.22200144166667</v>
+        <v>39.17738511666667</v>
       </c>
       <c r="R55">
-        <v>1.127659574468085</v>
+        <v>1.173913043478261</v>
       </c>
       <c r="S55">
-        <v>0.1627007438132816</v>
+        <v>0.164728808069257</v>
       </c>
       <c r="T55">
-        <v>1.701048261707431</v>
+        <v>1.730559067753013</v>
       </c>
       <c r="U55">
         <v>0.0535</v>
@@ -5823,7 +5823,7 @@
         </is>
       </c>
       <c r="Y55">
-        <v>8.832821849725754</v>
+        <v>8.669251074730834</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -5831,22 +5831,22 @@
     </row>
     <row r="56">
       <c r="A56">
-        <v>0.54</v>
+        <v>0.55</v>
       </c>
       <c r="B56">
-        <v>0.09455375171185823</v>
+        <v>0.09420740383147412</v>
       </c>
       <c r="C56">
-        <v>77.86659384449703</v>
+        <v>77.58805365972331</v>
       </c>
       <c r="D56">
-        <v>140.3885938444971</v>
+        <v>141.3930536597233</v>
       </c>
       <c r="E56">
-        <v>-3.717999999999989</v>
+        <v>-2.434999999999988</v>
       </c>
       <c r="F56">
-        <v>69.28200000000001</v>
+        <v>70.56500000000001</v>
       </c>
       <c r="G56">
         <v>6.76</v>
@@ -5867,28 +5867,28 @@
         <v>32.13333333333334</v>
       </c>
       <c r="M56">
-        <v>3.706587</v>
+        <v>3.775227500000001</v>
       </c>
       <c r="N56">
-        <v>28.42674633333334</v>
+        <v>28.35810583333334</v>
       </c>
       <c r="O56">
-        <v>9.949361216666668</v>
+        <v>9.925337041666669</v>
       </c>
       <c r="P56">
-        <v>18.47738511666667</v>
+        <v>18.43276879166667</v>
       </c>
       <c r="Q56">
-        <v>39.17738511666667</v>
+        <v>39.13276879166667</v>
       </c>
       <c r="R56">
-        <v>1.173913043478261</v>
+        <v>1.222222222222223</v>
       </c>
       <c r="S56">
-        <v>0.164728808069257</v>
+        <v>0.166847008514387</v>
       </c>
       <c r="T56">
-        <v>1.730559067753013</v>
+        <v>1.761381465178399</v>
       </c>
       <c r="U56">
         <v>0.0535</v>
@@ -5905,7 +5905,7 @@
         </is>
       </c>
       <c r="Y56">
-        <v>8.669251074730834</v>
+        <v>8.511628327917546</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -5913,22 +5913,22 @@
     </row>
     <row r="57">
       <c r="A57">
-        <v>0.55</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="B57">
-        <v>0.09420740383147412</v>
+        <v>0.09386105595109002</v>
       </c>
       <c r="C57">
-        <v>77.58805365972331</v>
+        <v>77.32399058208131</v>
       </c>
       <c r="D57">
-        <v>141.3930536597233</v>
+        <v>142.4119905820813</v>
       </c>
       <c r="E57">
-        <v>-2.434999999999988</v>
+        <v>-1.151999999999987</v>
       </c>
       <c r="F57">
-        <v>70.56500000000001</v>
+        <v>71.84800000000001</v>
       </c>
       <c r="G57">
         <v>6.76</v>
@@ -5949,28 +5949,28 @@
         <v>32.13333333333334</v>
       </c>
       <c r="M57">
-        <v>3.775227500000001</v>
+        <v>3.843868000000001</v>
       </c>
       <c r="N57">
-        <v>28.35810583333334</v>
+        <v>28.28946533333334</v>
       </c>
       <c r="O57">
-        <v>9.925337041666669</v>
+        <v>9.901312866666668</v>
       </c>
       <c r="P57">
-        <v>18.43276879166667</v>
+        <v>18.38815246666667</v>
       </c>
       <c r="Q57">
-        <v>39.13276879166667</v>
+        <v>39.08815246666667</v>
       </c>
       <c r="R57">
-        <v>1.222222222222223</v>
+        <v>1.272727272727273</v>
       </c>
       <c r="S57">
-        <v>0.166847008514387</v>
+        <v>0.1690614907979319</v>
       </c>
       <c r="T57">
-        <v>1.761381465178399</v>
+        <v>1.793604880668575</v>
       </c>
       <c r="U57">
         <v>0.0535</v>
@@ -5987,7 +5987,7 @@
         </is>
       </c>
       <c r="Y57">
-        <v>8.511628327917546</v>
+        <v>8.359634964919017</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -5995,22 +5995,22 @@
     </row>
     <row r="58">
       <c r="A58">
-        <v>0.5600000000000001</v>
+        <v>0.5700000000000001</v>
       </c>
       <c r="B58">
-        <v>0.09386105595109002</v>
+        <v>0.09351470807070592</v>
       </c>
       <c r="C58">
-        <v>77.32399058208131</v>
+        <v>77.0747198675313</v>
       </c>
       <c r="D58">
-        <v>142.4119905820813</v>
+        <v>143.4457198675313</v>
       </c>
       <c r="E58">
-        <v>-1.151999999999987</v>
+        <v>0.1310000000000144</v>
       </c>
       <c r="F58">
-        <v>71.84800000000001</v>
+        <v>73.13100000000001</v>
       </c>
       <c r="G58">
         <v>6.76</v>
@@ -6031,28 +6031,28 @@
         <v>32.13333333333334</v>
       </c>
       <c r="M58">
-        <v>3.843868000000001</v>
+        <v>3.912508500000001</v>
       </c>
       <c r="N58">
-        <v>28.28946533333334</v>
+        <v>28.22082483333334</v>
       </c>
       <c r="O58">
-        <v>9.901312866666668</v>
+        <v>9.877288691666667</v>
       </c>
       <c r="P58">
-        <v>18.38815246666667</v>
+        <v>18.34353614166667</v>
       </c>
       <c r="Q58">
-        <v>39.08815246666667</v>
+        <v>39.04353614166667</v>
       </c>
       <c r="R58">
-        <v>1.272727272727273</v>
+        <v>1.325581395348838</v>
       </c>
       <c r="S58">
-        <v>0.1690614907979319</v>
+        <v>0.1713789722574557</v>
       </c>
       <c r="T58">
-        <v>1.793604880668575</v>
+        <v>1.827327059669922</v>
       </c>
       <c r="U58">
         <v>0.0535</v>
@@ -6069,7 +6069,7 @@
         </is>
       </c>
       <c r="Y58">
-        <v>8.359634964919017</v>
+        <v>8.212974702376577</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6077,22 +6077,22 @@
     </row>
     <row r="59">
       <c r="A59">
-        <v>0.5700000000000001</v>
+        <v>0.5800000000000001</v>
       </c>
       <c r="B59">
-        <v>0.09351470807070592</v>
+        <v>0.09316836019032183</v>
       </c>
       <c r="C59">
-        <v>77.0747198675313</v>
+        <v>76.84056599238491</v>
       </c>
       <c r="D59">
-        <v>143.4457198675313</v>
+        <v>144.4945659923849</v>
       </c>
       <c r="E59">
-        <v>0.1310000000000144</v>
+        <v>1.414000000000016</v>
       </c>
       <c r="F59">
-        <v>73.13100000000001</v>
+        <v>74.41400000000002</v>
       </c>
       <c r="G59">
         <v>6.76</v>
@@ -6113,28 +6113,28 @@
         <v>32.13333333333334</v>
       </c>
       <c r="M59">
-        <v>3.912508500000001</v>
+        <v>3.981149000000001</v>
       </c>
       <c r="N59">
-        <v>28.22082483333334</v>
+        <v>28.15218433333334</v>
       </c>
       <c r="O59">
-        <v>9.877288691666667</v>
+        <v>9.853264516666668</v>
       </c>
       <c r="P59">
-        <v>18.34353614166667</v>
+        <v>18.29891981666667</v>
       </c>
       <c r="Q59">
-        <v>39.04353614166667</v>
+        <v>38.99891981666667</v>
       </c>
       <c r="R59">
-        <v>1.325581395348838</v>
+        <v>1.380952380952381</v>
       </c>
       <c r="S59">
-        <v>0.1713789722574557</v>
+        <v>0.1738068099769568</v>
       </c>
       <c r="T59">
-        <v>1.827327059669922</v>
+        <v>1.862655056718953</v>
       </c>
       <c r="U59">
         <v>0.0535</v>
@@ -6151,7 +6151,7 @@
         </is>
       </c>
       <c r="Y59">
-        <v>8.212974702376577</v>
+        <v>8.071371690266638</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6159,22 +6159,22 @@
     </row>
     <row r="60">
       <c r="A60">
-        <v>0.58</v>
+        <v>0.59</v>
       </c>
       <c r="B60">
-        <v>0.09316836019032185</v>
+        <v>0.09282201230993774</v>
       </c>
       <c r="C60">
-        <v>76.84056599238487</v>
+        <v>76.62186299287515</v>
       </c>
       <c r="D60">
-        <v>144.4945659923849</v>
+        <v>145.5588629928752</v>
       </c>
       <c r="E60">
-        <v>1.414000000000001</v>
+        <v>2.697000000000003</v>
       </c>
       <c r="F60">
-        <v>74.414</v>
+        <v>75.697</v>
       </c>
       <c r="G60">
         <v>6.76</v>
@@ -6195,28 +6195,28 @@
         <v>32.13333333333334</v>
       </c>
       <c r="M60">
-        <v>3.981149</v>
+        <v>4.0497895</v>
       </c>
       <c r="N60">
-        <v>28.15218433333334</v>
+        <v>28.08354383333334</v>
       </c>
       <c r="O60">
-        <v>9.85326451666667</v>
+        <v>9.829240341666669</v>
       </c>
       <c r="P60">
-        <v>18.29891981666667</v>
+        <v>18.25430349166667</v>
       </c>
       <c r="Q60">
-        <v>38.99891981666667</v>
+        <v>38.95430349166667</v>
       </c>
       <c r="R60">
-        <v>1.380952380952381</v>
+        <v>1.439024390243902</v>
       </c>
       <c r="S60">
-        <v>0.1738068099769567</v>
+        <v>0.1763530788047262</v>
       </c>
       <c r="T60">
-        <v>1.862655056718953</v>
+        <v>1.899706370697204</v>
       </c>
       <c r="U60">
         <v>0.0535</v>
@@ -6233,7 +6233,7 @@
         </is>
       </c>
       <c r="Y60">
-        <v>8.071371690266639</v>
+        <v>7.934568780262119</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6241,22 +6241,22 @@
     </row>
     <row r="61">
       <c r="A61">
-        <v>0.59</v>
+        <v>0.6</v>
       </c>
       <c r="B61">
-        <v>0.09282201230993774</v>
+        <v>0.09247566442955364</v>
       </c>
       <c r="C61">
-        <v>76.62186299287515</v>
+        <v>76.41895481984402</v>
       </c>
       <c r="D61">
-        <v>145.5588629928752</v>
+        <v>146.638954819844</v>
       </c>
       <c r="E61">
-        <v>2.697000000000003</v>
+        <v>3.980000000000004</v>
       </c>
       <c r="F61">
-        <v>75.697</v>
+        <v>76.98</v>
       </c>
       <c r="G61">
         <v>6.76</v>
@@ -6277,28 +6277,28 @@
         <v>32.13333333333334</v>
       </c>
       <c r="M61">
-        <v>4.0497895</v>
+        <v>4.11843</v>
       </c>
       <c r="N61">
-        <v>28.08354383333334</v>
+        <v>28.01490333333334</v>
       </c>
       <c r="O61">
-        <v>9.829240341666669</v>
+        <v>9.805216166666668</v>
       </c>
       <c r="P61">
-        <v>18.25430349166667</v>
+        <v>18.20968716666667</v>
       </c>
       <c r="Q61">
-        <v>38.95430349166667</v>
+        <v>38.90968716666667</v>
       </c>
       <c r="R61">
-        <v>1.439024390243902</v>
+        <v>1.5</v>
       </c>
       <c r="S61">
-        <v>0.1763530788047262</v>
+        <v>0.1790266610738841</v>
       </c>
       <c r="T61">
-        <v>1.899706370697204</v>
+        <v>1.938610250374368</v>
       </c>
       <c r="U61">
         <v>0.0535</v>
@@ -6315,7 +6315,7 @@
         </is>
       </c>
       <c r="Y61">
-        <v>7.934568780262119</v>
+        <v>7.802325967257751</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6323,22 +6323,22 @@
     </row>
     <row r="62">
       <c r="A62">
-        <v>0.6</v>
+        <v>0.61</v>
       </c>
       <c r="B62">
-        <v>0.09247566442955364</v>
+        <v>0.09212931654916955</v>
       </c>
       <c r="C62">
-        <v>76.41895481984402</v>
+        <v>76.23219570933975</v>
       </c>
       <c r="D62">
-        <v>146.638954819844</v>
+        <v>147.7351957093398</v>
       </c>
       <c r="E62">
-        <v>3.980000000000004</v>
+        <v>5.263000000000005</v>
       </c>
       <c r="F62">
-        <v>76.98</v>
+        <v>78.26300000000001</v>
       </c>
       <c r="G62">
         <v>6.76</v>
@@ -6359,28 +6359,28 @@
         <v>32.13333333333334</v>
       </c>
       <c r="M62">
-        <v>4.11843</v>
+        <v>4.1870705</v>
       </c>
       <c r="N62">
-        <v>28.01490333333334</v>
+        <v>27.94626283333334</v>
       </c>
       <c r="O62">
-        <v>9.805216166666668</v>
+        <v>9.781191991666669</v>
       </c>
       <c r="P62">
-        <v>18.20968716666667</v>
+        <v>18.16507084166667</v>
       </c>
       <c r="Q62">
-        <v>38.90968716666667</v>
+        <v>38.86507084166666</v>
       </c>
       <c r="R62">
-        <v>1.5</v>
+        <v>1.564102564102564</v>
       </c>
       <c r="S62">
-        <v>0.1790266610738841</v>
+        <v>0.1818373501260757</v>
       </c>
       <c r="T62">
-        <v>1.938610250374368</v>
+        <v>1.979509200804207</v>
       </c>
       <c r="U62">
         <v>0.0535</v>
@@ -6397,7 +6397,7 @@
         </is>
       </c>
       <c r="Y62">
-        <v>7.802325967257751</v>
+        <v>7.674418984187952</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6405,22 +6405,22 @@
     </row>
     <row r="63">
       <c r="A63">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="B63">
-        <v>0.09212931654916955</v>
+        <v>0.09210536866878544</v>
       </c>
       <c r="C63">
-        <v>76.23219570933975</v>
+        <v>75.02560034441949</v>
       </c>
       <c r="D63">
-        <v>147.7351957093398</v>
+        <v>147.8116003444195</v>
       </c>
       <c r="E63">
-        <v>5.263000000000005</v>
+        <v>6.546000000000006</v>
       </c>
       <c r="F63">
-        <v>78.26300000000001</v>
+        <v>79.54600000000001</v>
       </c>
       <c r="G63">
         <v>6.76</v>
@@ -6441,45 +6441,45 @@
         <v>32.13333333333334</v>
       </c>
       <c r="M63">
-        <v>4.1870705</v>
+        <v>4.3193478</v>
       </c>
       <c r="N63">
-        <v>27.94626283333334</v>
+        <v>27.81398553333334</v>
       </c>
       <c r="O63">
-        <v>9.781191991666669</v>
+        <v>9.734894936666668</v>
       </c>
       <c r="P63">
-        <v>18.16507084166667</v>
+        <v>18.07909059666667</v>
       </c>
       <c r="Q63">
-        <v>38.86507084166666</v>
+        <v>38.77909059666668</v>
       </c>
       <c r="R63">
-        <v>1.564102564102564</v>
+        <v>1.631578947368421</v>
       </c>
       <c r="S63">
-        <v>0.1818373501260757</v>
+        <v>0.1847959701810143</v>
       </c>
       <c r="T63">
-        <v>1.979509200804207</v>
+        <v>2.022560727572459</v>
       </c>
       <c r="U63">
-        <v>0.0535</v>
+        <v>0.0543</v>
       </c>
       <c r="V63">
         <v>0.35</v>
       </c>
       <c r="W63">
-        <v>0.034775</v>
+        <v>0.035295</v>
       </c>
       <c r="X63" t="inlineStr">
         <is>
-          <t>A1/A+</t>
+          <t>A2/A</t>
         </is>
       </c>
       <c r="Y63">
-        <v>7.674418984187952</v>
+        <v>7.4393947468952</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6487,22 +6487,22 @@
     </row>
     <row r="64">
       <c r="A64">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="B64">
-        <v>0.09210536866878544</v>
+        <v>0.09176422078840134</v>
       </c>
       <c r="C64">
-        <v>75.02560034441949</v>
+        <v>74.83966265263996</v>
       </c>
       <c r="D64">
-        <v>147.8116003444195</v>
+        <v>148.90866265264</v>
       </c>
       <c r="E64">
-        <v>6.546000000000006</v>
+        <v>7.829000000000008</v>
       </c>
       <c r="F64">
-        <v>79.54600000000001</v>
+        <v>80.82900000000001</v>
       </c>
       <c r="G64">
         <v>6.76</v>
@@ -6523,28 +6523,28 @@
         <v>32.13333333333334</v>
       </c>
       <c r="M64">
-        <v>4.3193478</v>
+        <v>4.389014700000001</v>
       </c>
       <c r="N64">
-        <v>27.81398553333334</v>
+        <v>27.74431863333334</v>
       </c>
       <c r="O64">
-        <v>9.734894936666668</v>
+        <v>9.710511521666668</v>
       </c>
       <c r="P64">
-        <v>18.07909059666667</v>
+        <v>18.03380711166667</v>
       </c>
       <c r="Q64">
-        <v>38.77909059666668</v>
+        <v>38.73380711166667</v>
       </c>
       <c r="R64">
-        <v>1.631578947368421</v>
+        <v>1.702702702702703</v>
       </c>
       <c r="S64">
-        <v>0.1847959701810143</v>
+        <v>0.187914515644328</v>
       </c>
       <c r="T64">
-        <v>2.022560727572459</v>
+        <v>2.067939363895751</v>
       </c>
       <c r="U64">
         <v>0.0543</v>
@@ -6561,7 +6561,7 @@
         </is>
       </c>
       <c r="Y64">
-        <v>7.4393947468952</v>
+        <v>7.321309115992101</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6569,22 +6569,22 @@
     </row>
     <row r="65">
       <c r="A65">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="B65">
-        <v>0.09176422078840134</v>
+        <v>0.09142307290801724</v>
       </c>
       <c r="C65">
-        <v>74.83966265263996</v>
+        <v>74.67013159273525</v>
       </c>
       <c r="D65">
-        <v>148.90866265264</v>
+        <v>150.0221315927353</v>
       </c>
       <c r="E65">
-        <v>7.829000000000008</v>
+        <v>9.112000000000009</v>
       </c>
       <c r="F65">
-        <v>80.82900000000001</v>
+        <v>82.11200000000001</v>
       </c>
       <c r="G65">
         <v>6.76</v>
@@ -6605,28 +6605,28 @@
         <v>32.13333333333334</v>
       </c>
       <c r="M65">
-        <v>4.389014700000001</v>
+        <v>4.4586816</v>
       </c>
       <c r="N65">
-        <v>27.74431863333334</v>
+        <v>27.67465173333334</v>
       </c>
       <c r="O65">
-        <v>9.710511521666668</v>
+        <v>9.686128106666668</v>
       </c>
       <c r="P65">
-        <v>18.03380711166667</v>
+        <v>17.98852362666667</v>
       </c>
       <c r="Q65">
-        <v>38.73380711166667</v>
+        <v>38.68852362666667</v>
       </c>
       <c r="R65">
-        <v>1.702702702702703</v>
+        <v>1.777777777777778</v>
       </c>
       <c r="S65">
-        <v>0.187914515644328</v>
+        <v>0.1912063136333813</v>
       </c>
       <c r="T65">
-        <v>2.067939363895751</v>
+        <v>2.115839035570337</v>
       </c>
       <c r="U65">
         <v>0.0543</v>
@@ -6643,7 +6643,7 @@
         </is>
       </c>
       <c r="Y65">
-        <v>7.321309115992101</v>
+        <v>7.206913661054725</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -6651,22 +6651,22 @@
     </row>
     <row r="66">
       <c r="A66">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="B66">
-        <v>0.09142307290801724</v>
+        <v>0.09108192502763314</v>
       </c>
       <c r="C66">
-        <v>74.67013159273525</v>
+        <v>74.51737798072193</v>
       </c>
       <c r="D66">
-        <v>150.0221315927353</v>
+        <v>151.152377980722</v>
       </c>
       <c r="E66">
-        <v>9.112000000000009</v>
+        <v>10.39500000000001</v>
       </c>
       <c r="F66">
-        <v>82.11200000000001</v>
+        <v>83.39500000000001</v>
       </c>
       <c r="G66">
         <v>6.76</v>
@@ -6687,28 +6687,28 @@
         <v>32.13333333333334</v>
       </c>
       <c r="M66">
-        <v>4.4586816</v>
+        <v>4.528348500000001</v>
       </c>
       <c r="N66">
-        <v>27.67465173333334</v>
+        <v>27.60498483333334</v>
       </c>
       <c r="O66">
-        <v>9.686128106666668</v>
+        <v>9.661744691666668</v>
       </c>
       <c r="P66">
-        <v>17.98852362666667</v>
+        <v>17.94324014166667</v>
       </c>
       <c r="Q66">
-        <v>38.68852362666667</v>
+        <v>38.64324014166667</v>
       </c>
       <c r="R66">
-        <v>1.777777777777778</v>
+        <v>1.857142857142857</v>
       </c>
       <c r="S66">
-        <v>0.1912063136333813</v>
+        <v>0.1946862143646661</v>
       </c>
       <c r="T66">
-        <v>2.115839035570337</v>
+        <v>2.166475831340614</v>
       </c>
       <c r="U66">
         <v>0.0543</v>
@@ -6725,7 +6725,7 @@
         </is>
       </c>
       <c r="Y66">
-        <v>7.206913661054725</v>
+        <v>7.096038066269267</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -6733,22 +6733,22 @@
     </row>
     <row r="67">
       <c r="A67">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="B67">
-        <v>0.09108192502763314</v>
+        <v>0.09074077714724904</v>
       </c>
       <c r="C67">
-        <v>74.51737798072193</v>
+        <v>74.38178389215476</v>
       </c>
       <c r="D67">
-        <v>151.152377980722</v>
+        <v>152.2997838921548</v>
       </c>
       <c r="E67">
-        <v>10.39500000000001</v>
+        <v>11.67800000000001</v>
       </c>
       <c r="F67">
-        <v>83.39500000000001</v>
+        <v>84.67800000000001</v>
       </c>
       <c r="G67">
         <v>6.76</v>
@@ -6769,28 +6769,28 @@
         <v>32.13333333333334</v>
       </c>
       <c r="M67">
-        <v>4.528348500000001</v>
+        <v>4.5980154</v>
       </c>
       <c r="N67">
-        <v>27.60498483333334</v>
+        <v>27.53531793333334</v>
       </c>
       <c r="O67">
-        <v>9.661744691666668</v>
+        <v>9.637361276666669</v>
       </c>
       <c r="P67">
-        <v>17.94324014166667</v>
+        <v>17.89795665666667</v>
       </c>
       <c r="Q67">
-        <v>38.64324014166667</v>
+        <v>38.59795665666667</v>
       </c>
       <c r="R67">
-        <v>1.857142857142857</v>
+        <v>1.941176470588236</v>
       </c>
       <c r="S67">
-        <v>0.1946862143646661</v>
+        <v>0.1983708151389678</v>
       </c>
       <c r="T67">
-        <v>2.166475831340614</v>
+        <v>2.220091262156201</v>
       </c>
       <c r="U67">
         <v>0.0543</v>
@@ -6807,7 +6807,7 @@
         </is>
       </c>
       <c r="Y67">
-        <v>7.096038066269267</v>
+        <v>6.98852233799246</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -6815,22 +6815,22 @@
     </row>
     <row r="68">
       <c r="A68">
-        <v>0.66</v>
+        <v>0.67</v>
       </c>
       <c r="B68">
-        <v>0.09074077714724904</v>
+        <v>0.09039962926686496</v>
       </c>
       <c r="C68">
-        <v>74.38178389215476</v>
+        <v>74.26374309275428</v>
       </c>
       <c r="D68">
-        <v>152.2997838921548</v>
+        <v>153.4647430927543</v>
       </c>
       <c r="E68">
-        <v>11.67800000000001</v>
+        <v>12.96100000000001</v>
       </c>
       <c r="F68">
-        <v>84.67800000000001</v>
+        <v>85.96100000000001</v>
       </c>
       <c r="G68">
         <v>6.76</v>
@@ -6851,28 +6851,28 @@
         <v>32.13333333333334</v>
       </c>
       <c r="M68">
-        <v>4.5980154</v>
+        <v>4.667682300000001</v>
       </c>
       <c r="N68">
-        <v>27.53531793333334</v>
+        <v>27.46565103333334</v>
       </c>
       <c r="O68">
-        <v>9.637361276666669</v>
+        <v>9.612977861666668</v>
       </c>
       <c r="P68">
-        <v>17.89795665666667</v>
+        <v>17.85267317166667</v>
       </c>
       <c r="Q68">
-        <v>38.59795665666667</v>
+        <v>38.55267317166667</v>
       </c>
       <c r="R68">
-        <v>1.941176470588236</v>
+        <v>2.030303030303031</v>
       </c>
       <c r="S68">
-        <v>0.1983708151389678</v>
+        <v>0.2022787250511059</v>
       </c>
       <c r="T68">
-        <v>2.220091262156201</v>
+        <v>2.276956113021218</v>
       </c>
       <c r="U68">
         <v>0.0543</v>
@@ -6889,7 +6889,7 @@
         </is>
       </c>
       <c r="Y68">
-        <v>6.98852233799246</v>
+        <v>6.884216034440333</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -6897,22 +6897,22 @@
     </row>
     <row r="69">
       <c r="A69">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="B69">
-        <v>0.09039962926686496</v>
+        <v>0.09005848138648086</v>
       </c>
       <c r="C69">
-        <v>74.26374309275428</v>
+        <v>74.16366148895067</v>
       </c>
       <c r="D69">
-        <v>153.4647430927543</v>
+        <v>154.6476614889507</v>
       </c>
       <c r="E69">
-        <v>12.96100000000001</v>
+        <v>14.24400000000001</v>
       </c>
       <c r="F69">
-        <v>85.96100000000001</v>
+        <v>87.24400000000001</v>
       </c>
       <c r="G69">
         <v>6.76</v>
@@ -6933,28 +6933,28 @@
         <v>32.13333333333334</v>
       </c>
       <c r="M69">
-        <v>4.667682300000001</v>
+        <v>4.737349200000001</v>
       </c>
       <c r="N69">
-        <v>27.46565103333334</v>
+        <v>27.39598413333334</v>
       </c>
       <c r="O69">
-        <v>9.612977861666668</v>
+        <v>9.588594446666669</v>
       </c>
       <c r="P69">
-        <v>17.85267317166667</v>
+        <v>17.80738968666667</v>
       </c>
       <c r="Q69">
-        <v>38.55267317166667</v>
+        <v>38.50738968666667</v>
       </c>
       <c r="R69">
-        <v>2.030303030303031</v>
+        <v>2.125</v>
       </c>
       <c r="S69">
-        <v>0.2022787250511059</v>
+        <v>0.2064308793327527</v>
       </c>
       <c r="T69">
-        <v>2.276956113021218</v>
+        <v>2.337375017065299</v>
       </c>
       <c r="U69">
         <v>0.0543</v>
@@ -6971,7 +6971,7 @@
         </is>
       </c>
       <c r="Y69">
-        <v>6.884216034440333</v>
+        <v>6.782977563345623</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -6979,22 +6979,22 @@
     </row>
     <row r="70">
       <c r="A70">
-        <v>0.68</v>
+        <v>0.6900000000000001</v>
       </c>
       <c r="B70">
-        <v>0.09005848138648086</v>
+        <v>0.08971733350609674</v>
       </c>
       <c r="C70">
-        <v>74.16366148895067</v>
+        <v>74.08195759942583</v>
       </c>
       <c r="D70">
-        <v>154.6476614889507</v>
+        <v>155.8489575994259</v>
       </c>
       <c r="E70">
-        <v>14.24400000000001</v>
+        <v>15.52700000000002</v>
       </c>
       <c r="F70">
-        <v>87.24400000000001</v>
+        <v>88.52700000000002</v>
       </c>
       <c r="G70">
         <v>6.76</v>
@@ -7015,28 +7015,28 @@
         <v>32.13333333333334</v>
       </c>
       <c r="M70">
-        <v>4.737349200000001</v>
+        <v>4.807016100000001</v>
       </c>
       <c r="N70">
-        <v>27.39598413333334</v>
+        <v>27.32631723333334</v>
       </c>
       <c r="O70">
-        <v>9.588594446666669</v>
+        <v>9.564211031666668</v>
       </c>
       <c r="P70">
-        <v>17.80738968666667</v>
+        <v>17.76210620166667</v>
       </c>
       <c r="Q70">
-        <v>38.50738968666667</v>
+        <v>38.46210620166667</v>
       </c>
       <c r="R70">
-        <v>2.125</v>
+        <v>2.225806451612904</v>
       </c>
       <c r="S70">
-        <v>0.2064308793327527</v>
+        <v>0.210850914535796</v>
       </c>
       <c r="T70">
-        <v>2.337375017065299</v>
+        <v>2.401691914918674</v>
       </c>
       <c r="U70">
         <v>0.0543</v>
@@ -7053,7 +7053,7 @@
         </is>
       </c>
       <c r="Y70">
-        <v>6.782977563345623</v>
+        <v>6.684673540688439</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7061,22 +7061,22 @@
     </row>
     <row r="71">
       <c r="A71">
-        <v>0.6900000000000001</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="B71">
-        <v>0.08971733350609674</v>
+        <v>0.08937618562571266</v>
       </c>
       <c r="C71">
-        <v>74.08195759942583</v>
+        <v>74.01906304880556</v>
       </c>
       <c r="D71">
-        <v>155.8489575994259</v>
+        <v>157.0690630488056</v>
       </c>
       <c r="E71">
-        <v>15.52700000000002</v>
+        <v>16.81000000000002</v>
       </c>
       <c r="F71">
-        <v>88.52700000000002</v>
+        <v>89.81000000000002</v>
       </c>
       <c r="G71">
         <v>6.76</v>
@@ -7097,28 +7097,28 @@
         <v>32.13333333333334</v>
       </c>
       <c r="M71">
-        <v>4.807016100000001</v>
+        <v>4.876683000000001</v>
       </c>
       <c r="N71">
-        <v>27.32631723333334</v>
+        <v>27.25665033333334</v>
       </c>
       <c r="O71">
-        <v>9.564211031666668</v>
+        <v>9.539827616666669</v>
       </c>
       <c r="P71">
-        <v>17.76210620166667</v>
+        <v>17.71682271666667</v>
       </c>
       <c r="Q71">
-        <v>38.46210620166667</v>
+        <v>38.41682271666667</v>
       </c>
       <c r="R71">
-        <v>2.225806451612904</v>
+        <v>2.333333333333334</v>
       </c>
       <c r="S71">
-        <v>0.210850914535796</v>
+        <v>0.2155656187523755</v>
       </c>
       <c r="T71">
-        <v>2.401691914918674</v>
+        <v>2.470296605962275</v>
       </c>
       <c r="U71">
         <v>0.0543</v>
@@ -7135,7 +7135,7 @@
         </is>
       </c>
       <c r="Y71">
-        <v>6.684673540688439</v>
+        <v>6.589178204392891</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7143,22 +7143,22 @@
     </row>
     <row r="72">
       <c r="A72">
-        <v>0.7000000000000001</v>
+        <v>0.7100000000000001</v>
       </c>
       <c r="B72">
-        <v>0.08937618562571266</v>
+        <v>0.08903503774532856</v>
       </c>
       <c r="C72">
-        <v>74.01906304880556</v>
+        <v>73.97542308472472</v>
       </c>
       <c r="D72">
-        <v>157.0690630488056</v>
+        <v>158.3084230847248</v>
       </c>
       <c r="E72">
-        <v>16.81000000000002</v>
+        <v>18.09300000000002</v>
       </c>
       <c r="F72">
-        <v>89.81000000000002</v>
+        <v>91.09300000000002</v>
       </c>
       <c r="G72">
         <v>6.76</v>
@@ -7179,28 +7179,28 @@
         <v>32.13333333333334</v>
       </c>
       <c r="M72">
-        <v>4.876683000000001</v>
+        <v>4.946349900000001</v>
       </c>
       <c r="N72">
-        <v>27.25665033333334</v>
+        <v>27.18698343333334</v>
       </c>
       <c r="O72">
-        <v>9.539827616666669</v>
+        <v>9.515444201666668</v>
       </c>
       <c r="P72">
-        <v>17.71682271666667</v>
+        <v>17.67153923166667</v>
       </c>
       <c r="Q72">
-        <v>38.41682271666667</v>
+        <v>38.37153923166667</v>
       </c>
       <c r="R72">
-        <v>2.333333333333334</v>
+        <v>2.448275862068967</v>
       </c>
       <c r="S72">
-        <v>0.2155656187523755</v>
+        <v>0.2206054749838916</v>
       </c>
       <c r="T72">
-        <v>2.470296605962275</v>
+        <v>2.543632655008883</v>
       </c>
       <c r="U72">
         <v>0.0543</v>
@@ -7217,7 +7217,7 @@
         </is>
       </c>
       <c r="Y72">
-        <v>6.589178204392891</v>
+        <v>6.496372877570455</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7225,22 +7225,22 @@
     </row>
     <row r="73">
       <c r="A73">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="B73">
-        <v>0.08903503774532856</v>
+        <v>0.08869388986494446</v>
       </c>
       <c r="C73">
-        <v>73.97542308472474</v>
+        <v>73.95149711956623</v>
       </c>
       <c r="D73">
-        <v>158.3084230847248</v>
+        <v>159.5674971195662</v>
       </c>
       <c r="E73">
-        <v>18.093</v>
+        <v>19.376</v>
       </c>
       <c r="F73">
-        <v>91.093</v>
+        <v>92.376</v>
       </c>
       <c r="G73">
         <v>6.76</v>
@@ -7261,28 +7261,28 @@
         <v>32.13333333333334</v>
       </c>
       <c r="M73">
-        <v>4.9463499</v>
+        <v>5.0160168</v>
       </c>
       <c r="N73">
-        <v>27.18698343333334</v>
+        <v>27.11731653333334</v>
       </c>
       <c r="O73">
-        <v>9.515444201666668</v>
+        <v>9.491060786666669</v>
       </c>
       <c r="P73">
-        <v>17.67153923166667</v>
+        <v>17.62625574666667</v>
       </c>
       <c r="Q73">
-        <v>38.37153923166667</v>
+        <v>38.32625574666667</v>
       </c>
       <c r="R73">
-        <v>2.448275862068965</v>
+        <v>2.571428571428571</v>
       </c>
       <c r="S73">
-        <v>0.2206054749838915</v>
+        <v>0.2260053209462302</v>
       </c>
       <c r="T73">
-        <v>2.543632655008882</v>
+        <v>2.622206993273105</v>
       </c>
       <c r="U73">
         <v>0.0543</v>
@@ -7299,7 +7299,7 @@
         </is>
       </c>
       <c r="Y73">
-        <v>6.496372877570455</v>
+        <v>6.406145476493089</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7307,22 +7307,22 @@
     </row>
     <row r="74">
       <c r="A74">
-        <v>0.72</v>
+        <v>0.73</v>
       </c>
       <c r="B74">
-        <v>0.08869388986494446</v>
+        <v>0.08835274198456036</v>
       </c>
       <c r="C74">
-        <v>73.95149711956623</v>
+        <v>73.94775929825936</v>
       </c>
       <c r="D74">
-        <v>159.5674971195662</v>
+        <v>160.8467592982594</v>
       </c>
       <c r="E74">
-        <v>19.376</v>
+        <v>20.65900000000001</v>
       </c>
       <c r="F74">
-        <v>92.376</v>
+        <v>93.65900000000001</v>
       </c>
       <c r="G74">
         <v>6.76</v>
@@ -7343,28 +7343,28 @@
         <v>32.13333333333334</v>
       </c>
       <c r="M74">
-        <v>5.0160168</v>
+        <v>5.085683700000001</v>
       </c>
       <c r="N74">
-        <v>27.11731653333334</v>
+        <v>27.04764963333334</v>
       </c>
       <c r="O74">
-        <v>9.491060786666669</v>
+        <v>9.466677371666668</v>
       </c>
       <c r="P74">
-        <v>17.62625574666667</v>
+        <v>17.58097226166667</v>
       </c>
       <c r="Q74">
-        <v>38.32625574666667</v>
+        <v>38.28097226166668</v>
       </c>
       <c r="R74">
-        <v>2.571428571428571</v>
+        <v>2.703703703703703</v>
       </c>
       <c r="S74">
-        <v>0.2260053209462302</v>
+        <v>0.2318051554983717</v>
       </c>
       <c r="T74">
-        <v>2.622206993273105</v>
+        <v>2.706601652890233</v>
       </c>
       <c r="U74">
         <v>0.0543</v>
@@ -7381,7 +7381,7 @@
         </is>
       </c>
       <c r="Y74">
-        <v>6.406145476493089</v>
+        <v>6.318390059006882</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7389,22 +7389,22 @@
     </row>
     <row r="75">
       <c r="A75">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="B75">
-        <v>0.08835274198456036</v>
+        <v>0.08801159410417626</v>
       </c>
       <c r="C75">
-        <v>73.94775929825936</v>
+        <v>73.96469909361107</v>
       </c>
       <c r="D75">
-        <v>160.8467592982594</v>
+        <v>162.1466990936111</v>
       </c>
       <c r="E75">
-        <v>20.65900000000001</v>
+        <v>21.94200000000001</v>
       </c>
       <c r="F75">
-        <v>93.65900000000001</v>
+        <v>94.94200000000001</v>
       </c>
       <c r="G75">
         <v>6.76</v>
@@ -7425,28 +7425,28 @@
         <v>32.13333333333334</v>
       </c>
       <c r="M75">
-        <v>5.085683700000001</v>
+        <v>5.1553506</v>
       </c>
       <c r="N75">
-        <v>27.04764963333334</v>
+        <v>26.97798273333334</v>
       </c>
       <c r="O75">
-        <v>9.466677371666668</v>
+        <v>9.442293956666669</v>
       </c>
       <c r="P75">
-        <v>17.58097226166667</v>
+        <v>17.53568877666667</v>
       </c>
       <c r="Q75">
-        <v>38.28097226166668</v>
+        <v>38.23568877666668</v>
       </c>
       <c r="R75">
-        <v>2.703703703703703</v>
+        <v>2.846153846153846</v>
       </c>
       <c r="S75">
-        <v>0.2318051554983717</v>
+        <v>0.2380511311699087</v>
       </c>
       <c r="T75">
-        <v>2.706601652890233</v>
+        <v>2.797488209400986</v>
       </c>
       <c r="U75">
         <v>0.0543</v>
@@ -7463,7 +7463,7 @@
         </is>
       </c>
       <c r="Y75">
-        <v>6.318390059006882</v>
+        <v>6.233006409560844</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7471,22 +7471,22 @@
     </row>
     <row r="76">
       <c r="A76">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="B76">
-        <v>0.08801159410417626</v>
+        <v>0.08767044622379216</v>
       </c>
       <c r="C76">
-        <v>73.96469909361107</v>
+        <v>74.00282193074081</v>
       </c>
       <c r="D76">
-        <v>162.1466990936111</v>
+        <v>163.4678219307408</v>
       </c>
       <c r="E76">
-        <v>21.94200000000001</v>
+        <v>23.22500000000001</v>
       </c>
       <c r="F76">
-        <v>94.94200000000001</v>
+        <v>96.22500000000001</v>
       </c>
       <c r="G76">
         <v>6.76</v>
@@ -7507,28 +7507,28 @@
         <v>32.13333333333334</v>
       </c>
       <c r="M76">
-        <v>5.1553506</v>
+        <v>5.225017500000001</v>
       </c>
       <c r="N76">
-        <v>26.97798273333334</v>
+        <v>26.90831583333334</v>
       </c>
       <c r="O76">
-        <v>9.442293956666669</v>
+        <v>9.417910541666668</v>
       </c>
       <c r="P76">
-        <v>17.53568877666667</v>
+        <v>17.49040529166667</v>
       </c>
       <c r="Q76">
-        <v>38.23568877666668</v>
+        <v>38.19040529166667</v>
       </c>
       <c r="R76">
-        <v>2.846153846153846</v>
+        <v>3</v>
       </c>
       <c r="S76">
-        <v>0.2380511311699087</v>
+        <v>0.2447967848951687</v>
       </c>
       <c r="T76">
-        <v>2.797488209400986</v>
+        <v>2.8956456904326</v>
       </c>
       <c r="U76">
         <v>0.0543</v>
@@ -7545,7 +7545,7 @@
         </is>
       </c>
       <c r="Y76">
-        <v>6.233006409560844</v>
+        <v>6.149899657433365</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7553,22 +7553,22 @@
     </row>
     <row r="77">
       <c r="A77">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="B77">
-        <v>0.08767044622379216</v>
+        <v>0.08782329834340806</v>
       </c>
       <c r="C77">
-        <v>74.00282193074081</v>
+        <v>72.12523740129902</v>
       </c>
       <c r="D77">
-        <v>163.4678219307408</v>
+        <v>162.873237401299</v>
       </c>
       <c r="E77">
-        <v>23.22500000000001</v>
+        <v>24.50800000000001</v>
       </c>
       <c r="F77">
-        <v>96.22500000000001</v>
+        <v>97.50800000000001</v>
       </c>
       <c r="G77">
         <v>6.76</v>
@@ -7589,45 +7589,45 @@
         <v>32.13333333333334</v>
       </c>
       <c r="M77">
-        <v>5.225017500000001</v>
+        <v>5.392192400000001</v>
       </c>
       <c r="N77">
-        <v>26.90831583333334</v>
+        <v>26.74114093333334</v>
       </c>
       <c r="O77">
-        <v>9.417910541666668</v>
+        <v>9.359399326666669</v>
       </c>
       <c r="P77">
-        <v>17.49040529166667</v>
+        <v>17.38174160666667</v>
       </c>
       <c r="Q77">
-        <v>38.19040529166667</v>
+        <v>38.08174160666667</v>
       </c>
       <c r="R77">
-        <v>3</v>
+        <v>3.166666666666667</v>
       </c>
       <c r="S77">
-        <v>0.2447967848951687</v>
+        <v>0.2521045764308669</v>
       </c>
       <c r="T77">
-        <v>2.8956456904326</v>
+        <v>3.001982961550182</v>
       </c>
       <c r="U77">
-        <v>0.0543</v>
+        <v>0.0553</v>
       </c>
       <c r="V77">
         <v>0.35</v>
       </c>
       <c r="W77">
-        <v>0.035295</v>
+        <v>0.035945</v>
       </c>
       <c r="X77" t="inlineStr">
         <is>
-          <t>A2/A</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y77">
-        <v>6.149899657433365</v>
+        <v>5.959233452673784</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -7635,22 +7635,22 @@
     </row>
     <row r="78">
       <c r="A78">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="B78">
-        <v>0.08782329834340806</v>
+        <v>0.08748865046302395</v>
       </c>
       <c r="C78">
-        <v>72.12523740129902</v>
+        <v>72.14967199230325</v>
       </c>
       <c r="D78">
-        <v>162.873237401299</v>
+        <v>164.1806719923033</v>
       </c>
       <c r="E78">
-        <v>24.50800000000001</v>
+        <v>25.79100000000001</v>
       </c>
       <c r="F78">
-        <v>97.50800000000001</v>
+        <v>98.79100000000001</v>
       </c>
       <c r="G78">
         <v>6.76</v>
@@ -7671,28 +7671,28 @@
         <v>32.13333333333334</v>
       </c>
       <c r="M78">
-        <v>5.392192400000001</v>
+        <v>5.463142300000001</v>
       </c>
       <c r="N78">
-        <v>26.74114093333334</v>
+        <v>26.67019103333334</v>
       </c>
       <c r="O78">
-        <v>9.359399326666669</v>
+        <v>9.334566861666667</v>
       </c>
       <c r="P78">
-        <v>17.38174160666667</v>
+        <v>17.33562417166667</v>
       </c>
       <c r="Q78">
-        <v>38.08174160666667</v>
+        <v>38.03562417166667</v>
       </c>
       <c r="R78">
-        <v>3.166666666666667</v>
+        <v>3.347826086956522</v>
       </c>
       <c r="S78">
-        <v>0.2521045764308669</v>
+        <v>0.2600478281001042</v>
       </c>
       <c r="T78">
-        <v>3.001982961550182</v>
+        <v>3.117566951895379</v>
       </c>
       <c r="U78">
         <v>0.0553</v>
@@ -7709,7 +7709,7 @@
         </is>
       </c>
       <c r="Y78">
-        <v>5.959233452673784</v>
+        <v>5.881840810431266</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -7717,22 +7717,22 @@
     </row>
     <row r="79">
       <c r="A79">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="B79">
-        <v>0.08748865046302395</v>
+        <v>0.08715400258263986</v>
       </c>
       <c r="C79">
-        <v>72.14967199230325</v>
+        <v>72.19526681870406</v>
       </c>
       <c r="D79">
-        <v>164.1806719923033</v>
+        <v>165.5092668187041</v>
       </c>
       <c r="E79">
-        <v>25.79100000000001</v>
+        <v>27.07400000000001</v>
       </c>
       <c r="F79">
-        <v>98.79100000000001</v>
+        <v>100.074</v>
       </c>
       <c r="G79">
         <v>6.76</v>
@@ -7753,28 +7753,28 @@
         <v>32.13333333333334</v>
       </c>
       <c r="M79">
-        <v>5.463142300000001</v>
+        <v>5.534092200000001</v>
       </c>
       <c r="N79">
-        <v>26.67019103333334</v>
+        <v>26.59924113333334</v>
       </c>
       <c r="O79">
-        <v>9.334566861666667</v>
+        <v>9.309734396666668</v>
       </c>
       <c r="P79">
-        <v>17.33562417166667</v>
+        <v>17.28950673666667</v>
       </c>
       <c r="Q79">
-        <v>38.03562417166667</v>
+        <v>37.98950673666667</v>
       </c>
       <c r="R79">
-        <v>3.347826086956522</v>
+        <v>3.545454545454546</v>
       </c>
       <c r="S79">
-        <v>0.2600478281001042</v>
+        <v>0.2687131935574539</v>
       </c>
       <c r="T79">
-        <v>3.117566951895379</v>
+        <v>3.243658577726503</v>
       </c>
       <c r="U79">
         <v>0.0553</v>
@@ -7791,7 +7791,7 @@
         </is>
       </c>
       <c r="Y79">
-        <v>5.881840810431266</v>
+        <v>5.806432594912917</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -7799,22 +7799,22 @@
     </row>
     <row r="80">
       <c r="A80">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="B80">
-        <v>0.08715400258263986</v>
+        <v>0.08681935470225577</v>
       </c>
       <c r="C80">
-        <v>72.19526681870406</v>
+        <v>72.26253977464985</v>
       </c>
       <c r="D80">
-        <v>165.5092668187041</v>
+        <v>166.8595397746499</v>
       </c>
       <c r="E80">
-        <v>27.07400000000001</v>
+        <v>28.35700000000001</v>
       </c>
       <c r="F80">
-        <v>100.074</v>
+        <v>101.357</v>
       </c>
       <c r="G80">
         <v>6.76</v>
@@ -7835,28 +7835,28 @@
         <v>32.13333333333334</v>
       </c>
       <c r="M80">
-        <v>5.534092200000001</v>
+        <v>5.605042100000001</v>
       </c>
       <c r="N80">
-        <v>26.59924113333334</v>
+        <v>26.52829123333334</v>
       </c>
       <c r="O80">
-        <v>9.309734396666668</v>
+        <v>9.284901931666667</v>
       </c>
       <c r="P80">
-        <v>17.28950673666667</v>
+        <v>17.24338930166667</v>
       </c>
       <c r="Q80">
-        <v>37.98950673666667</v>
+        <v>37.94338930166667</v>
       </c>
       <c r="R80">
-        <v>3.545454545454546</v>
+        <v>3.761904761904763</v>
       </c>
       <c r="S80">
-        <v>0.2687131935574539</v>
+        <v>0.2782038319155037</v>
       </c>
       <c r="T80">
-        <v>3.243658577726503</v>
+        <v>3.381758929827259</v>
       </c>
       <c r="U80">
         <v>0.0553</v>
@@ -7873,7 +7873,7 @@
         </is>
       </c>
       <c r="Y80">
-        <v>5.806432594912917</v>
+        <v>5.732933448141867</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -7881,22 +7881,22 @@
     </row>
     <row r="81">
       <c r="A81">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="B81">
-        <v>0.08681935470225577</v>
+        <v>0.08648470682187165</v>
       </c>
       <c r="C81">
-        <v>72.26253977464985</v>
+        <v>72.35202579382982</v>
       </c>
       <c r="D81">
-        <v>166.8595397746499</v>
+        <v>168.2320257938298</v>
       </c>
       <c r="E81">
-        <v>28.35700000000001</v>
+        <v>29.64000000000001</v>
       </c>
       <c r="F81">
-        <v>101.357</v>
+        <v>102.64</v>
       </c>
       <c r="G81">
         <v>6.76</v>
@@ -7917,28 +7917,28 @@
         <v>32.13333333333334</v>
       </c>
       <c r="M81">
-        <v>5.605042100000001</v>
+        <v>5.675992000000001</v>
       </c>
       <c r="N81">
-        <v>26.52829123333334</v>
+        <v>26.45734133333334</v>
       </c>
       <c r="O81">
-        <v>9.284901931666667</v>
+        <v>9.260069466666668</v>
       </c>
       <c r="P81">
-        <v>17.24338930166667</v>
+        <v>17.19727186666667</v>
       </c>
       <c r="Q81">
-        <v>37.94338930166667</v>
+        <v>37.89727186666667</v>
       </c>
       <c r="R81">
-        <v>3.761904761904763</v>
+        <v>4.000000000000001</v>
       </c>
       <c r="S81">
-        <v>0.2782038319155037</v>
+        <v>0.2886435341093583</v>
       </c>
       <c r="T81">
-        <v>3.381758929827259</v>
+        <v>3.533669317138089</v>
       </c>
       <c r="U81">
         <v>0.0553</v>
@@ -7955,7 +7955,7 @@
         </is>
       </c>
       <c r="Y81">
-        <v>5.732933448141867</v>
+        <v>5.661271780040094</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -7963,22 +7963,22 @@
     </row>
     <row r="82">
       <c r="A82">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="B82">
-        <v>0.08648470682187165</v>
+        <v>0.08615005894148757</v>
       </c>
       <c r="C82">
-        <v>72.35202579382982</v>
+        <v>72.46427755607051</v>
       </c>
       <c r="D82">
-        <v>168.2320257938298</v>
+        <v>169.6272775560705</v>
       </c>
       <c r="E82">
-        <v>29.64000000000001</v>
+        <v>30.92300000000002</v>
       </c>
       <c r="F82">
-        <v>102.64</v>
+        <v>103.923</v>
       </c>
       <c r="G82">
         <v>6.76</v>
@@ -7999,28 +7999,28 @@
         <v>32.13333333333334</v>
       </c>
       <c r="M82">
-        <v>5.675992000000001</v>
+        <v>5.746941900000001</v>
       </c>
       <c r="N82">
-        <v>26.45734133333334</v>
+        <v>26.38639143333334</v>
       </c>
       <c r="O82">
-        <v>9.260069466666668</v>
+        <v>9.235237001666667</v>
       </c>
       <c r="P82">
-        <v>17.19727186666667</v>
+        <v>17.15115443166667</v>
       </c>
       <c r="Q82">
-        <v>37.89727186666667</v>
+        <v>37.85115443166667</v>
       </c>
       <c r="R82">
-        <v>4.000000000000001</v>
+        <v>4.263157894736843</v>
       </c>
       <c r="S82">
-        <v>0.2886435341093583</v>
+        <v>0.3001821523236188</v>
       </c>
       <c r="T82">
-        <v>3.533669317138089</v>
+        <v>3.70157027153427</v>
       </c>
       <c r="U82">
         <v>0.0553</v>
@@ -8037,7 +8037,7 @@
         </is>
       </c>
       <c r="Y82">
-        <v>5.661271780040094</v>
+        <v>5.591379535842067</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8045,22 +8045,22 @@
     </row>
     <row r="83">
       <c r="A83">
-        <v>0.8100000000000001</v>
+        <v>0.8200000000000001</v>
       </c>
       <c r="B83">
-        <v>0.08615005894148757</v>
+        <v>0.08581541106110346</v>
       </c>
       <c r="C83">
-        <v>72.46427755607051</v>
+        <v>72.59986622938899</v>
       </c>
       <c r="D83">
-        <v>169.6272775560705</v>
+        <v>171.045866229389</v>
       </c>
       <c r="E83">
-        <v>30.92300000000002</v>
+        <v>32.20600000000002</v>
       </c>
       <c r="F83">
-        <v>103.923</v>
+        <v>105.206</v>
       </c>
       <c r="G83">
         <v>6.76</v>
@@ -8081,28 +8081,28 @@
         <v>32.13333333333334</v>
       </c>
       <c r="M83">
-        <v>5.746941900000001</v>
+        <v>5.817891800000001</v>
       </c>
       <c r="N83">
-        <v>26.38639143333334</v>
+        <v>26.31544153333334</v>
       </c>
       <c r="O83">
-        <v>9.235237001666667</v>
+        <v>9.210404536666667</v>
       </c>
       <c r="P83">
-        <v>17.15115443166667</v>
+        <v>17.10503699666667</v>
       </c>
       <c r="Q83">
-        <v>37.85115443166667</v>
+        <v>37.80503699666667</v>
       </c>
       <c r="R83">
-        <v>4.263157894736843</v>
+        <v>4.555555555555557</v>
       </c>
       <c r="S83">
-        <v>0.3001821523236188</v>
+        <v>0.3130028392283527</v>
       </c>
       <c r="T83">
-        <v>3.70157027153427</v>
+        <v>3.888126887530027</v>
       </c>
       <c r="U83">
         <v>0.0553</v>
@@ -8119,7 +8119,7 @@
         </is>
       </c>
       <c r="Y83">
-        <v>5.591379535842067</v>
+        <v>5.523191980526922</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8127,22 +8127,22 @@
     </row>
     <row r="84">
       <c r="A84">
-        <v>0.8200000000000001</v>
+        <v>0.8300000000000001</v>
       </c>
       <c r="B84">
-        <v>0.08581541106110346</v>
+        <v>0.08548076318071939</v>
       </c>
       <c r="C84">
-        <v>72.59986622938899</v>
+        <v>72.75938224959337</v>
       </c>
       <c r="D84">
-        <v>171.045866229389</v>
+        <v>172.4883822495934</v>
       </c>
       <c r="E84">
-        <v>32.20600000000002</v>
+        <v>33.48900000000002</v>
       </c>
       <c r="F84">
-        <v>105.206</v>
+        <v>106.489</v>
       </c>
       <c r="G84">
         <v>6.76</v>
@@ -8163,28 +8163,28 @@
         <v>32.13333333333334</v>
       </c>
       <c r="M84">
-        <v>5.817891800000001</v>
+        <v>5.888841700000001</v>
       </c>
       <c r="N84">
-        <v>26.31544153333334</v>
+        <v>26.24449163333334</v>
       </c>
       <c r="O84">
-        <v>9.210404536666667</v>
+        <v>9.185572071666668</v>
       </c>
       <c r="P84">
-        <v>17.10503699666667</v>
+        <v>17.05891956166667</v>
       </c>
       <c r="Q84">
-        <v>37.80503699666667</v>
+        <v>37.75891956166667</v>
       </c>
       <c r="R84">
-        <v>4.555555555555557</v>
+        <v>4.882352941176473</v>
       </c>
       <c r="S84">
-        <v>0.3130028392283527</v>
+        <v>0.3273318422395259</v>
       </c>
       <c r="T84">
-        <v>3.888126887530027</v>
+        <v>4.096631340701757</v>
       </c>
       <c r="U84">
         <v>0.0553</v>
@@ -8201,7 +8201,7 @@
         </is>
       </c>
       <c r="Y84">
-        <v>5.523191980526922</v>
+        <v>5.456647498833826</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8209,22 +8209,22 @@
     </row>
     <row r="85">
       <c r="A85">
-        <v>0.8300000000000001</v>
+        <v>0.8400000000000001</v>
       </c>
       <c r="B85">
-        <v>0.08548076318071939</v>
+        <v>0.08514611530033528</v>
       </c>
       <c r="C85">
-        <v>72.75938224959337</v>
+        <v>72.94343613966871</v>
       </c>
       <c r="D85">
-        <v>172.4883822495934</v>
+        <v>173.9554361396687</v>
       </c>
       <c r="E85">
-        <v>33.48900000000002</v>
+        <v>34.77200000000002</v>
       </c>
       <c r="F85">
-        <v>106.489</v>
+        <v>107.772</v>
       </c>
       <c r="G85">
         <v>6.76</v>
@@ -8245,28 +8245,28 @@
         <v>32.13333333333334</v>
       </c>
       <c r="M85">
-        <v>5.888841700000001</v>
+        <v>5.959791600000002</v>
       </c>
       <c r="N85">
-        <v>26.24449163333334</v>
+        <v>26.17354173333334</v>
       </c>
       <c r="O85">
-        <v>9.185572071666668</v>
+        <v>9.160739606666667</v>
       </c>
       <c r="P85">
-        <v>17.05891956166667</v>
+        <v>17.01280212666667</v>
       </c>
       <c r="Q85">
-        <v>37.75891956166667</v>
+        <v>37.71280212666667</v>
       </c>
       <c r="R85">
-        <v>4.882352941176473</v>
+        <v>5.250000000000004</v>
       </c>
       <c r="S85">
-        <v>0.3273318422395259</v>
+        <v>0.3434519706270956</v>
       </c>
       <c r="T85">
-        <v>4.096631340701757</v>
+        <v>4.331198850519951</v>
       </c>
       <c r="U85">
         <v>0.0553</v>
@@ -8283,7 +8283,7 @@
         </is>
       </c>
       <c r="Y85">
-        <v>5.456647498833826</v>
+        <v>5.391687409561993</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8291,22 +8291,22 @@
     </row>
     <row r="86">
       <c r="A86">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="B86">
-        <v>0.08514611530033528</v>
+        <v>0.08481146741995119</v>
       </c>
       <c r="C86">
-        <v>72.94343613966872</v>
+        <v>73.15265937133469</v>
       </c>
       <c r="D86">
-        <v>173.9554361396687</v>
+        <v>175.4476593713347</v>
       </c>
       <c r="E86">
-        <v>34.77200000000001</v>
+        <v>36.05500000000001</v>
       </c>
       <c r="F86">
-        <v>107.772</v>
+        <v>109.055</v>
       </c>
       <c r="G86">
         <v>6.76</v>
@@ -8327,28 +8327,28 @@
         <v>32.13333333333334</v>
       </c>
       <c r="M86">
-        <v>5.959791600000001</v>
+        <v>6.0307415</v>
       </c>
       <c r="N86">
-        <v>26.17354173333334</v>
+        <v>26.10259183333334</v>
       </c>
       <c r="O86">
-        <v>9.160739606666667</v>
+        <v>9.135907141666667</v>
       </c>
       <c r="P86">
-        <v>17.01280212666667</v>
+        <v>16.96668469166667</v>
       </c>
       <c r="Q86">
-        <v>37.71280212666667</v>
+        <v>37.66668469166667</v>
       </c>
       <c r="R86">
-        <v>5.249999999999999</v>
+        <v>5.666666666666666</v>
       </c>
       <c r="S86">
-        <v>0.3434519706270954</v>
+        <v>0.3617214494663412</v>
       </c>
       <c r="T86">
-        <v>4.331198850519948</v>
+        <v>4.597042028313902</v>
       </c>
       <c r="U86">
         <v>0.0553</v>
@@ -8365,7 +8365,7 @@
         </is>
       </c>
       <c r="Y86">
-        <v>5.391687409561994</v>
+        <v>5.328255792978912</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8373,22 +8373,22 @@
     </row>
     <row r="87">
       <c r="A87">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="B87">
-        <v>0.08481146741995119</v>
+        <v>0.08447681953956709</v>
       </c>
       <c r="C87">
-        <v>73.15265937133469</v>
+        <v>73.38770527133177</v>
       </c>
       <c r="D87">
-        <v>175.4476593713347</v>
+        <v>176.9657052713318</v>
       </c>
       <c r="E87">
-        <v>36.05500000000001</v>
+        <v>37.33800000000001</v>
       </c>
       <c r="F87">
-        <v>109.055</v>
+        <v>110.338</v>
       </c>
       <c r="G87">
         <v>6.76</v>
@@ -8409,28 +8409,28 @@
         <v>32.13333333333334</v>
       </c>
       <c r="M87">
-        <v>6.0307415</v>
+        <v>6.101691400000001</v>
       </c>
       <c r="N87">
-        <v>26.10259183333334</v>
+        <v>26.03164193333334</v>
       </c>
       <c r="O87">
-        <v>9.135907141666667</v>
+        <v>9.111074676666668</v>
       </c>
       <c r="P87">
-        <v>16.96668469166667</v>
+        <v>16.92056725666667</v>
       </c>
       <c r="Q87">
-        <v>37.66668469166667</v>
+        <v>37.62056725666667</v>
       </c>
       <c r="R87">
-        <v>5.666666666666666</v>
+        <v>6.142857142857142</v>
       </c>
       <c r="S87">
-        <v>0.3617214494663412</v>
+        <v>0.3826008538540506</v>
       </c>
       <c r="T87">
-        <v>4.597042028313902</v>
+        <v>4.900862802935563</v>
       </c>
       <c r="U87">
         <v>0.0553</v>
@@ -8447,7 +8447,7 @@
         </is>
       </c>
       <c r="Y87">
-        <v>5.328255792978912</v>
+        <v>5.266299330269855</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8455,22 +8455,22 @@
     </row>
     <row r="88">
       <c r="A88">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="B88">
-        <v>0.08447681953956709</v>
+        <v>0.08414217165918297</v>
       </c>
       <c r="C88">
-        <v>73.38770527133177</v>
+        <v>73.64924997516701</v>
       </c>
       <c r="D88">
-        <v>176.9657052713318</v>
+        <v>178.510249975167</v>
       </c>
       <c r="E88">
-        <v>37.33800000000001</v>
+        <v>38.62100000000001</v>
       </c>
       <c r="F88">
-        <v>110.338</v>
+        <v>111.621</v>
       </c>
       <c r="G88">
         <v>6.76</v>
@@ -8491,28 +8491,28 @@
         <v>32.13333333333334</v>
       </c>
       <c r="M88">
-        <v>6.101691400000001</v>
+        <v>6.1726413</v>
       </c>
       <c r="N88">
-        <v>26.03164193333334</v>
+        <v>25.96069203333334</v>
       </c>
       <c r="O88">
-        <v>9.111074676666668</v>
+        <v>9.086242211666667</v>
       </c>
       <c r="P88">
-        <v>16.92056725666667</v>
+        <v>16.87444982166667</v>
       </c>
       <c r="Q88">
-        <v>37.62056725666667</v>
+        <v>37.57444982166668</v>
       </c>
       <c r="R88">
-        <v>6.142857142857142</v>
+        <v>6.692307692307692</v>
       </c>
       <c r="S88">
-        <v>0.3826008538540506</v>
+        <v>0.4066924743014075</v>
       </c>
       <c r="T88">
-        <v>4.900862802935563</v>
+        <v>5.251425235191325</v>
       </c>
       <c r="U88">
         <v>0.0553</v>
@@ -8529,7 +8529,7 @@
         </is>
       </c>
       <c r="Y88">
-        <v>5.266299330269855</v>
+        <v>5.205767154059857</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8537,22 +8537,22 @@
     </row>
     <row r="89">
       <c r="A89">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="B89">
-        <v>0.08414217165918297</v>
+        <v>0.0838075237787989</v>
       </c>
       <c r="C89">
-        <v>73.64924997516701</v>
+        <v>73.9379934312441</v>
       </c>
       <c r="D89">
-        <v>178.510249975167</v>
+        <v>180.0819934312441</v>
       </c>
       <c r="E89">
-        <v>38.62100000000001</v>
+        <v>39.90400000000001</v>
       </c>
       <c r="F89">
-        <v>111.621</v>
+        <v>112.904</v>
       </c>
       <c r="G89">
         <v>6.76</v>
@@ -8573,28 +8573,28 @@
         <v>32.13333333333334</v>
       </c>
       <c r="M89">
-        <v>6.1726413</v>
+        <v>6.243591200000001</v>
       </c>
       <c r="N89">
-        <v>25.96069203333334</v>
+        <v>25.88974213333334</v>
       </c>
       <c r="O89">
-        <v>9.086242211666667</v>
+        <v>9.061409746666667</v>
       </c>
       <c r="P89">
-        <v>16.87444982166667</v>
+        <v>16.82833238666667</v>
       </c>
       <c r="Q89">
-        <v>37.57444982166668</v>
+        <v>37.52833238666668</v>
       </c>
       <c r="R89">
-        <v>6.692307692307692</v>
+        <v>7.333333333333334</v>
       </c>
       <c r="S89">
-        <v>0.4066924743014075</v>
+        <v>0.4347993648233241</v>
       </c>
       <c r="T89">
-        <v>5.251425235191325</v>
+        <v>5.660414739489717</v>
       </c>
       <c r="U89">
         <v>0.0553</v>
@@ -8611,7 +8611,7 @@
         </is>
       </c>
       <c r="Y89">
-        <v>5.205767154059857</v>
+        <v>5.146610709127359</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -8619,22 +8619,22 @@
     </row>
     <row r="90">
       <c r="A90">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="B90">
-        <v>0.0838075237787989</v>
+        <v>0.08347287589841479</v>
       </c>
       <c r="C90">
-        <v>73.9379934312441</v>
+        <v>74.2546604585136</v>
       </c>
       <c r="D90">
-        <v>180.0819934312441</v>
+        <v>181.6816604585136</v>
       </c>
       <c r="E90">
-        <v>39.90400000000001</v>
+        <v>41.18700000000001</v>
       </c>
       <c r="F90">
-        <v>112.904</v>
+        <v>114.187</v>
       </c>
       <c r="G90">
         <v>6.76</v>
@@ -8655,28 +8655,28 @@
         <v>32.13333333333334</v>
       </c>
       <c r="M90">
-        <v>6.243591200000001</v>
+        <v>6.3145411</v>
       </c>
       <c r="N90">
-        <v>25.88974213333334</v>
+        <v>25.81879223333334</v>
       </c>
       <c r="O90">
-        <v>9.061409746666667</v>
+        <v>9.036577281666668</v>
       </c>
       <c r="P90">
-        <v>16.82833238666667</v>
+        <v>16.78221495166667</v>
       </c>
       <c r="Q90">
-        <v>37.52833238666668</v>
+        <v>37.48221495166668</v>
       </c>
       <c r="R90">
-        <v>7.333333333333334</v>
+        <v>8.090909090909092</v>
       </c>
       <c r="S90">
-        <v>0.4347993648233241</v>
+        <v>0.4680165990764981</v>
       </c>
       <c r="T90">
-        <v>5.660414739489717</v>
+        <v>6.143765971842359</v>
       </c>
       <c r="U90">
         <v>0.0553</v>
@@ -8693,7 +8693,7 @@
         </is>
       </c>
       <c r="Y90">
-        <v>5.146610709127359</v>
+        <v>5.08878362250795</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -8701,22 +8701,22 @@
     </row>
     <row r="91">
       <c r="A91">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="B91">
-        <v>0.08347287589841479</v>
+        <v>0.0831382280180307</v>
       </c>
       <c r="C91">
-        <v>74.2546604585136</v>
+        <v>74.60000186099644</v>
       </c>
       <c r="D91">
-        <v>181.6816604585136</v>
+        <v>183.3100018609965</v>
       </c>
       <c r="E91">
-        <v>41.18700000000001</v>
+        <v>42.47000000000001</v>
       </c>
       <c r="F91">
-        <v>114.187</v>
+        <v>115.47</v>
       </c>
       <c r="G91">
         <v>6.76</v>
@@ -8737,28 +8737,28 @@
         <v>32.13333333333334</v>
       </c>
       <c r="M91">
-        <v>6.3145411</v>
+        <v>6.385491000000001</v>
       </c>
       <c r="N91">
-        <v>25.81879223333334</v>
+        <v>25.74784233333334</v>
       </c>
       <c r="O91">
-        <v>9.036577281666668</v>
+        <v>9.011744816666667</v>
       </c>
       <c r="P91">
-        <v>16.78221495166667</v>
+        <v>16.73609751666667</v>
       </c>
       <c r="Q91">
-        <v>37.48221495166668</v>
+        <v>37.43609751666667</v>
       </c>
       <c r="R91">
-        <v>8.090909090909092</v>
+        <v>9.000000000000002</v>
       </c>
       <c r="S91">
-        <v>0.4680165990764981</v>
+        <v>0.507877280180307</v>
       </c>
       <c r="T91">
-        <v>6.143765971842359</v>
+        <v>6.723787450665531</v>
       </c>
       <c r="U91">
         <v>0.0553</v>
@@ -8775,7 +8775,7 @@
         </is>
       </c>
       <c r="Y91">
-        <v>5.08878362250795</v>
+        <v>5.032241582257861</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -8783,22 +8783,22 @@
     </row>
     <row r="92">
       <c r="A92">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="B92">
-        <v>0.0831382280180307</v>
+        <v>0.08280358013764658</v>
       </c>
       <c r="C92">
-        <v>74.60000186099644</v>
+        <v>74.97479560278578</v>
       </c>
       <c r="D92">
-        <v>183.3100018609965</v>
+        <v>184.9677956027858</v>
       </c>
       <c r="E92">
-        <v>42.47000000000001</v>
+        <v>43.75300000000001</v>
       </c>
       <c r="F92">
-        <v>115.47</v>
+        <v>116.753</v>
       </c>
       <c r="G92">
         <v>6.76</v>
@@ -8819,28 +8819,28 @@
         <v>32.13333333333334</v>
       </c>
       <c r="M92">
-        <v>6.385491000000001</v>
+        <v>6.456440900000001</v>
       </c>
       <c r="N92">
-        <v>25.74784233333334</v>
+        <v>25.67689243333334</v>
       </c>
       <c r="O92">
-        <v>9.011744816666667</v>
+        <v>8.986912351666668</v>
       </c>
       <c r="P92">
-        <v>16.73609751666667</v>
+        <v>16.68998008166667</v>
       </c>
       <c r="Q92">
-        <v>37.43609751666667</v>
+        <v>37.38998008166667</v>
       </c>
       <c r="R92">
-        <v>9.000000000000002</v>
+        <v>10.11111111111111</v>
       </c>
       <c r="S92">
-        <v>0.507877280180307</v>
+        <v>0.5565958904182955</v>
       </c>
       <c r="T92">
-        <v>6.723787450665531</v>
+        <v>7.432702591449408</v>
       </c>
       <c r="U92">
         <v>0.0553</v>
@@ -8857,7 +8857,7 @@
         </is>
       </c>
       <c r="Y92">
-        <v>5.032241582257861</v>
+        <v>4.976942224211072</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -8865,22 +8865,22 @@
     </row>
     <row r="93">
       <c r="A93">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="B93">
-        <v>0.08280358013764658</v>
+        <v>0.0824689322572625</v>
       </c>
       <c r="C93">
-        <v>74.97479560278578</v>
+        <v>75.37984804738697</v>
       </c>
       <c r="D93">
-        <v>184.9677956027858</v>
+        <v>186.655848047387</v>
       </c>
       <c r="E93">
-        <v>43.75300000000001</v>
+        <v>45.03600000000002</v>
       </c>
       <c r="F93">
-        <v>116.753</v>
+        <v>118.036</v>
       </c>
       <c r="G93">
         <v>6.76</v>
@@ -8901,28 +8901,28 @@
         <v>32.13333333333334</v>
       </c>
       <c r="M93">
-        <v>6.456440900000001</v>
+        <v>6.527390800000001</v>
       </c>
       <c r="N93">
-        <v>25.67689243333334</v>
+        <v>25.60594253333334</v>
       </c>
       <c r="O93">
-        <v>8.986912351666668</v>
+        <v>8.962079886666668</v>
       </c>
       <c r="P93">
-        <v>16.68998008166667</v>
+        <v>16.64386264666667</v>
       </c>
       <c r="Q93">
-        <v>37.38998008166667</v>
+        <v>37.34386264666667</v>
       </c>
       <c r="R93">
-        <v>10.11111111111111</v>
+        <v>11.50000000000001</v>
       </c>
       <c r="S93">
-        <v>0.5565958904182955</v>
+        <v>0.6174941532157815</v>
       </c>
       <c r="T93">
-        <v>7.432702591449408</v>
+        <v>8.318846517429256</v>
       </c>
       <c r="U93">
         <v>0.0553</v>
@@ -8939,7 +8939,7 @@
         </is>
       </c>
       <c r="Y93">
-        <v>4.976942224211072</v>
+        <v>4.922845026121822</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -8947,22 +8947,22 @@
     </row>
     <row r="94">
       <c r="A94">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="B94">
-        <v>0.0824689322572625</v>
+        <v>0.08213428437687838</v>
       </c>
       <c r="C94">
-        <v>75.37984804738697</v>
+        <v>75.8159952655474</v>
       </c>
       <c r="D94">
-        <v>186.655848047387</v>
+        <v>188.3749952655474</v>
       </c>
       <c r="E94">
-        <v>45.03600000000002</v>
+        <v>46.31900000000002</v>
       </c>
       <c r="F94">
-        <v>118.036</v>
+        <v>119.319</v>
       </c>
       <c r="G94">
         <v>6.76</v>
@@ -8983,28 +8983,28 @@
         <v>32.13333333333334</v>
       </c>
       <c r="M94">
-        <v>6.527390800000001</v>
+        <v>6.598340700000001</v>
       </c>
       <c r="N94">
-        <v>25.60594253333334</v>
+        <v>25.53499263333334</v>
       </c>
       <c r="O94">
-        <v>8.962079886666668</v>
+        <v>8.937247421666667</v>
       </c>
       <c r="P94">
-        <v>16.64386264666667</v>
+        <v>16.59774521166667</v>
       </c>
       <c r="Q94">
-        <v>37.34386264666667</v>
+        <v>37.29774521166667</v>
       </c>
       <c r="R94">
-        <v>11.50000000000001</v>
+        <v>13.2857142857143</v>
       </c>
       <c r="S94">
-        <v>0.6174941532157815</v>
+        <v>0.6957919196696916</v>
       </c>
       <c r="T94">
-        <v>8.318846517429256</v>
+        <v>9.458174422260484</v>
       </c>
       <c r="U94">
         <v>0.0553</v>
@@ -9021,7 +9021,7 @@
         </is>
       </c>
       <c r="Y94">
-        <v>4.922845026121822</v>
+        <v>4.869911208636641</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9029,22 +9029,22 @@
     </row>
     <row r="95">
       <c r="A95">
-        <v>0.93</v>
+        <v>0.9400000000000001</v>
       </c>
       <c r="B95">
-        <v>0.08213428437687838</v>
+        <v>0.0817996364964943</v>
       </c>
       <c r="C95">
-        <v>75.8159952655474</v>
+        <v>76.28410441602769</v>
       </c>
       <c r="D95">
-        <v>188.3749952655474</v>
+        <v>190.1261044160277</v>
       </c>
       <c r="E95">
-        <v>46.31900000000002</v>
+        <v>47.60200000000002</v>
       </c>
       <c r="F95">
-        <v>119.319</v>
+        <v>120.602</v>
       </c>
       <c r="G95">
         <v>6.76</v>
@@ -9065,28 +9065,28 @@
         <v>32.13333333333334</v>
       </c>
       <c r="M95">
-        <v>6.598340700000001</v>
+        <v>6.669290600000001</v>
       </c>
       <c r="N95">
-        <v>25.53499263333334</v>
+        <v>25.46404273333334</v>
       </c>
       <c r="O95">
-        <v>8.937247421666667</v>
+        <v>8.912414956666668</v>
       </c>
       <c r="P95">
-        <v>16.59774521166667</v>
+        <v>16.55162777666667</v>
       </c>
       <c r="Q95">
-        <v>37.29774521166667</v>
+        <v>37.25162777666667</v>
       </c>
       <c r="R95">
-        <v>13.2857142857143</v>
+        <v>15.66666666666668</v>
       </c>
       <c r="S95">
-        <v>0.6957919196696916</v>
+        <v>0.8001889416082388</v>
       </c>
       <c r="T95">
-        <v>9.458174422260484</v>
+        <v>10.97727829536879</v>
       </c>
       <c r="U95">
         <v>0.0553</v>
@@ -9103,7 +9103,7 @@
         </is>
       </c>
       <c r="Y95">
-        <v>4.869911208636641</v>
+        <v>4.818103642587315</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9111,22 +9111,22 @@
     </row>
     <row r="96">
       <c r="A96">
-        <v>0.9400000000000001</v>
+        <v>0.9500000000000001</v>
       </c>
       <c r="B96">
-        <v>0.0817996364964943</v>
+        <v>0.08146498861611021</v>
       </c>
       <c r="C96">
-        <v>76.28410441602769</v>
+        <v>76.78507520411225</v>
       </c>
       <c r="D96">
-        <v>190.1261044160277</v>
+        <v>191.9100752041123</v>
       </c>
       <c r="E96">
-        <v>47.60200000000002</v>
+        <v>48.88500000000002</v>
       </c>
       <c r="F96">
-        <v>120.602</v>
+        <v>121.885</v>
       </c>
       <c r="G96">
         <v>6.76</v>
@@ -9147,28 +9147,28 @@
         <v>32.13333333333334</v>
       </c>
       <c r="M96">
-        <v>6.669290600000001</v>
+        <v>6.740240500000001</v>
       </c>
       <c r="N96">
-        <v>25.46404273333334</v>
+        <v>25.39309283333334</v>
       </c>
       <c r="O96">
-        <v>8.912414956666668</v>
+        <v>8.887582491666668</v>
       </c>
       <c r="P96">
-        <v>16.55162777666667</v>
+        <v>16.50551034166667</v>
       </c>
       <c r="Q96">
-        <v>37.25162777666667</v>
+        <v>37.20551034166667</v>
       </c>
       <c r="R96">
-        <v>15.66666666666668</v>
+        <v>19.00000000000003</v>
       </c>
       <c r="S96">
-        <v>0.8001889416082388</v>
+        <v>0.9463447723222052</v>
       </c>
       <c r="T96">
-        <v>10.97727829536879</v>
+        <v>13.10402371772043</v>
       </c>
       <c r="U96">
         <v>0.0553</v>
@@ -9185,7 +9185,7 @@
         </is>
       </c>
       <c r="Y96">
-        <v>4.818103642587315</v>
+        <v>4.767386762139026</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9193,22 +9193,22 @@
     </row>
     <row r="97">
       <c r="A97">
-        <v>0.9500000000000001</v>
+        <v>0.9600000000000001</v>
       </c>
       <c r="B97">
-        <v>0.08146498861611021</v>
+        <v>0.0811303407357261</v>
       </c>
       <c r="C97">
-        <v>76.78507520411225</v>
+        <v>77.31984142300603</v>
       </c>
       <c r="D97">
-        <v>191.9100752041123</v>
+        <v>193.7278414230061</v>
       </c>
       <c r="E97">
-        <v>48.88500000000002</v>
+        <v>50.16800000000002</v>
       </c>
       <c r="F97">
-        <v>121.885</v>
+        <v>123.168</v>
       </c>
       <c r="G97">
         <v>6.76</v>
@@ -9229,28 +9229,28 @@
         <v>32.13333333333334</v>
       </c>
       <c r="M97">
-        <v>6.740240500000001</v>
+        <v>6.811190400000001</v>
       </c>
       <c r="N97">
-        <v>25.39309283333334</v>
+        <v>25.32214293333334</v>
       </c>
       <c r="O97">
-        <v>8.887582491666668</v>
+        <v>8.862750026666667</v>
       </c>
       <c r="P97">
-        <v>16.50551034166667</v>
+        <v>16.45939290666667</v>
       </c>
       <c r="Q97">
-        <v>37.20551034166667</v>
+        <v>37.15939290666667</v>
       </c>
       <c r="R97">
-        <v>19.00000000000003</v>
+        <v>24.00000000000005</v>
       </c>
       <c r="S97">
-        <v>0.9463447723222052</v>
+        <v>1.165578518393154</v>
       </c>
       <c r="T97">
-        <v>13.10402371772043</v>
+        <v>16.29414185124788</v>
       </c>
       <c r="U97">
         <v>0.0553</v>
@@ -9267,7 +9267,7 @@
         </is>
       </c>
       <c r="Y97">
-        <v>4.767386762139026</v>
+        <v>4.717726483366745</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9275,22 +9275,22 @@
     </row>
     <row r="98">
       <c r="A98">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="B98">
-        <v>0.08113034073572611</v>
+        <v>0.08079569285534202</v>
       </c>
       <c r="C98">
-        <v>77.31984142300598</v>
+        <v>77.88937258367129</v>
       </c>
       <c r="D98">
-        <v>193.727841423006</v>
+        <v>195.5803725836713</v>
       </c>
       <c r="E98">
-        <v>50.16800000000001</v>
+        <v>51.45100000000001</v>
       </c>
       <c r="F98">
-        <v>123.168</v>
+        <v>124.451</v>
       </c>
       <c r="G98">
         <v>6.76</v>
@@ -9311,28 +9311,28 @@
         <v>32.13333333333334</v>
       </c>
       <c r="M98">
-        <v>6.811190400000001</v>
+        <v>6.882140300000001</v>
       </c>
       <c r="N98">
-        <v>25.32214293333334</v>
+        <v>25.25119303333334</v>
       </c>
       <c r="O98">
-        <v>8.862750026666667</v>
+        <v>8.837917561666668</v>
       </c>
       <c r="P98">
-        <v>16.45939290666667</v>
+        <v>16.41327547166667</v>
       </c>
       <c r="Q98">
-        <v>37.15939290666667</v>
+        <v>37.11327547166667</v>
       </c>
       <c r="R98">
-        <v>23.99999999999998</v>
+        <v>32.33333333333331</v>
       </c>
       <c r="S98">
-        <v>1.165578518393152</v>
+        <v>1.530968095178066</v>
       </c>
       <c r="T98">
-        <v>16.29414185124784</v>
+        <v>21.61100540712691</v>
       </c>
       <c r="U98">
         <v>0.0553</v>
@@ -9349,7 +9349,7 @@
         </is>
       </c>
       <c r="Y98">
-        <v>4.717726483366745</v>
+        <v>4.669090127868119</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9357,22 +9357,22 @@
     </row>
     <row r="99">
       <c r="A99">
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
       <c r="B99">
-        <v>0.08079569285534202</v>
+        <v>0.0804610449749579</v>
       </c>
       <c r="C99">
-        <v>77.88937258367129</v>
+        <v>78.49467563907973</v>
       </c>
       <c r="D99">
-        <v>195.5803725836713</v>
+        <v>197.4686756390797</v>
       </c>
       <c r="E99">
-        <v>51.45100000000001</v>
+        <v>52.73400000000001</v>
       </c>
       <c r="F99">
-        <v>124.451</v>
+        <v>125.734</v>
       </c>
       <c r="G99">
         <v>6.76</v>
@@ -9393,28 +9393,28 @@
         <v>32.13333333333334</v>
       </c>
       <c r="M99">
-        <v>6.882140300000001</v>
+        <v>6.953090200000001</v>
       </c>
       <c r="N99">
-        <v>25.25119303333334</v>
+        <v>25.18024313333334</v>
       </c>
       <c r="O99">
-        <v>8.837917561666668</v>
+        <v>8.813085096666669</v>
       </c>
       <c r="P99">
-        <v>16.41327547166667</v>
+        <v>16.36715803666667</v>
       </c>
       <c r="Q99">
-        <v>37.11327547166667</v>
+        <v>37.06715803666667</v>
       </c>
       <c r="R99">
-        <v>32.33333333333331</v>
+        <v>48.99999999999996</v>
       </c>
       <c r="S99">
-        <v>1.530968095178066</v>
+        <v>2.261747248747893</v>
       </c>
       <c r="T99">
-        <v>21.61100540712691</v>
+        <v>32.24473251888503</v>
       </c>
       <c r="U99">
         <v>0.0553</v>
@@ -9431,7 +9431,7 @@
         </is>
       </c>
       <c r="Y99">
-        <v>4.669090127868119</v>
+        <v>4.621446351053138</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9439,22 +9439,22 @@
     </row>
     <row r="100">
       <c r="A100">
-        <v>0.98</v>
+        <v>0.99</v>
       </c>
       <c r="B100">
-        <v>0.0804610449749579</v>
+        <v>0.08012639709457381</v>
       </c>
       <c r="C100">
-        <v>78.49467563907973</v>
+        <v>79.13679680932101</v>
       </c>
       <c r="D100">
-        <v>197.4686756390797</v>
+        <v>199.393796809321</v>
       </c>
       <c r="E100">
-        <v>52.73400000000001</v>
+        <v>54.01700000000001</v>
       </c>
       <c r="F100">
-        <v>125.734</v>
+        <v>127.017</v>
       </c>
       <c r="G100">
         <v>6.76</v>
@@ -9475,28 +9475,28 @@
         <v>32.13333333333334</v>
       </c>
       <c r="M100">
-        <v>6.953090200000001</v>
+        <v>7.024040100000001</v>
       </c>
       <c r="N100">
-        <v>25.18024313333334</v>
+        <v>25.10929323333334</v>
       </c>
       <c r="O100">
-        <v>8.813085096666669</v>
+        <v>8.788252631666667</v>
       </c>
       <c r="P100">
-        <v>16.36715803666667</v>
+        <v>16.32104060166667</v>
       </c>
       <c r="Q100">
-        <v>37.06715803666667</v>
+        <v>37.02104060166667</v>
       </c>
       <c r="R100">
-        <v>48.99999999999996</v>
+        <v>98.99999999999991</v>
       </c>
       <c r="S100">
-        <v>2.261747248747893</v>
+        <v>4.454084709457376</v>
       </c>
       <c r="T100">
-        <v>32.24473251888503</v>
+        <v>64.14591385415942</v>
       </c>
       <c r="U100">
         <v>0.0553</v>
@@ -9513,91 +9513,9 @@
         </is>
       </c>
       <c r="Y100">
-        <v>4.621446351053138</v>
+        <v>4.574765074779874</v>
       </c>
       <c r="Z100">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101">
-        <v>0.99</v>
-      </c>
-      <c r="B101">
-        <v>0.08012639709457381</v>
-      </c>
-      <c r="C101">
-        <v>79.13679680932101</v>
-      </c>
-      <c r="D101">
-        <v>199.393796809321</v>
-      </c>
-      <c r="E101">
-        <v>54.01700000000001</v>
-      </c>
-      <c r="F101">
-        <v>127.017</v>
-      </c>
-      <c r="G101">
-        <v>6.76</v>
-      </c>
-      <c r="H101">
-        <v>55.3</v>
-      </c>
-      <c r="I101">
-        <v>0</v>
-      </c>
-      <c r="J101">
-        <v>52.83333333333334</v>
-      </c>
-      <c r="K101">
-        <v>20.7</v>
-      </c>
-      <c r="L101">
-        <v>32.13333333333334</v>
-      </c>
-      <c r="M101">
-        <v>7.024040100000001</v>
-      </c>
-      <c r="N101">
-        <v>25.10929323333334</v>
-      </c>
-      <c r="O101">
-        <v>8.788252631666667</v>
-      </c>
-      <c r="P101">
-        <v>16.32104060166667</v>
-      </c>
-      <c r="Q101">
-        <v>37.02104060166667</v>
-      </c>
-      <c r="R101">
-        <v>98.99999999999991</v>
-      </c>
-      <c r="S101">
-        <v>4.454084709457376</v>
-      </c>
-      <c r="T101">
-        <v>64.14591385415942</v>
-      </c>
-      <c r="U101">
-        <v>0.0553</v>
-      </c>
-      <c r="V101">
-        <v>0.35</v>
-      </c>
-      <c r="W101">
-        <v>0.035945</v>
-      </c>
-      <c r="X101" t="inlineStr">
-        <is>
-          <t>A3/A-</t>
-        </is>
-      </c>
-      <c r="Y101">
-        <v>4.574765074779874</v>
-      </c>
-      <c r="Z101">
         <v>0</v>
       </c>
     </row>
